--- a/players.xlsx
+++ b/players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5e5db209541c51e/Documents/GitHub/FantasyPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_2331BF95553D7991B99468D3475ED87656C26EAB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3B765B3-591E-49A1-B44F-A2959896E9AC}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_2331BF95553D7991B99468D3475ED87656C26EAB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C946E37-DBC5-4C34-85B7-FADA97A72BB8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18879,117 +18879,117 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>33.299999999999997</v>
+        <v>29.4</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D20">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20">
-        <v>31.2</v>
+        <v>28.6</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21">
         <v>20</v>
       </c>
-      <c r="D21">
-        <v>23</v>
-      </c>
       <c r="E21">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F21">
-        <v>30.3</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E22">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F22">
-        <v>29.4</v>
+        <v>31.2</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="D23">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E23">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="G23" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">

--- a/players.xlsx
+++ b/players.xlsx
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E57" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F57" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58">
@@ -2685,7 +2685,7 @@
         <v>29</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
@@ -2716,15 +2716,18 @@
         <v>63</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>1466</t>
         </is>
+      </c>
+      <c r="H67" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="68">
@@ -2747,15 +2750,18 @@
         <v>64</v>
       </c>
       <c r="E68" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>4199</t>
         </is>
+      </c>
+      <c r="H68" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="69">
@@ -2781,12 +2787,15 @@
         <v>25</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>12512</t>
         </is>
+      </c>
+      <c r="H69" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="70">
@@ -2809,15 +2818,18 @@
         <v>66</v>
       </c>
       <c r="E70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>11560</t>
         </is>
+      </c>
+      <c r="H70" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="71">
@@ -2837,18 +2849,21 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>10859</t>
         </is>
+      </c>
+      <c r="H71" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="72">
@@ -2868,18 +2883,21 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E72" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>7594</t>
         </is>
+      </c>
+      <c r="H72" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="73">
@@ -2902,15 +2920,18 @@
         <v>69</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>4943</t>
         </is>
+      </c>
+      <c r="H73" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="74">
@@ -2933,15 +2954,18 @@
         <v>70</v>
       </c>
       <c r="E74" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>9500</t>
         </is>
+      </c>
+      <c r="H74" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="75">
@@ -2961,18 +2985,21 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>4217</t>
         </is>
+      </c>
+      <c r="H75" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="76">
@@ -2995,15 +3022,18 @@
         <v>72</v>
       </c>
       <c r="E76" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>2216</t>
         </is>
+      </c>
+      <c r="H76" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="77">
@@ -3026,15 +3056,18 @@
         <v>73</v>
       </c>
       <c r="E77" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>11646</t>
         </is>
+      </c>
+      <c r="H77" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="78">
@@ -3060,12 +3093,15 @@
         <v>9</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>3294</t>
         </is>
+      </c>
+      <c r="H78" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="79">
@@ -3085,18 +3121,21 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E79" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>13286</t>
         </is>
+      </c>
+      <c r="H79" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="80">
@@ -3116,18 +3155,21 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>12506</t>
         </is>
+      </c>
+      <c r="H80" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="81">
@@ -3150,15 +3192,18 @@
         <v>77</v>
       </c>
       <c r="E81" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>8148</t>
         </is>
+      </c>
+      <c r="H81" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="82">
@@ -3181,15 +3226,18 @@
         <v>78</v>
       </c>
       <c r="E82" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>5872</t>
         </is>
+      </c>
+      <c r="H82" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="83">
@@ -3212,15 +3260,18 @@
         <v>79</v>
       </c>
       <c r="E83" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>5850</t>
         </is>
+      </c>
+      <c r="H83" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="84">
@@ -3240,18 +3291,21 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E84" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>10236</t>
         </is>
+      </c>
+      <c r="H84" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="85">
@@ -3274,10 +3328,10 @@
         <v>81</v>
       </c>
       <c r="E85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3305,18 +3359,21 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E86" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>7543</t>
         </is>
+      </c>
+      <c r="H86" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="87">
@@ -3339,15 +3396,18 @@
         <v>83</v>
       </c>
       <c r="E87" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>5967</t>
         </is>
+      </c>
+      <c r="H87" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="88">
@@ -3367,18 +3427,21 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E88" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>8126</t>
         </is>
+      </c>
+      <c r="H88" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="89">
@@ -3401,15 +3464,18 @@
         <v>85</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>12517</t>
         </is>
+      </c>
+      <c r="H89" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="90">
@@ -3432,15 +3498,18 @@
         <v>86</v>
       </c>
       <c r="E90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>9484</t>
         </is>
+      </c>
+      <c r="H90" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="91">
@@ -3460,18 +3529,21 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E91" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>12489</t>
         </is>
+      </c>
+      <c r="H91" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="92">
@@ -3494,15 +3566,18 @@
         <v>88</v>
       </c>
       <c r="E92" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>421</t>
         </is>
+      </c>
+      <c r="H92" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="93">
@@ -3522,18 +3597,21 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E93" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>2449</t>
         </is>
+      </c>
+      <c r="H93" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="94">
@@ -3553,18 +3631,21 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E94" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>13330</t>
         </is>
+      </c>
+      <c r="H94" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="95">
@@ -3584,13 +3665,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E95" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3598,7 +3679,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="96">
@@ -3618,10 +3699,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E96" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3652,15 +3733,18 @@
         <v>93</v>
       </c>
       <c r="E97" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>6806</t>
         </is>
+      </c>
+      <c r="H97" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="98">
@@ -3683,15 +3767,18 @@
         <v>94</v>
       </c>
       <c r="E98" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>8134</t>
         </is>
+      </c>
+      <c r="H98" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="99">
@@ -3711,18 +3798,21 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E99" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>5045</t>
         </is>
+      </c>
+      <c r="H99" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="100">
@@ -3742,18 +3832,21 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E100" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>4046</t>
         </is>
+      </c>
+      <c r="H100" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="101">
@@ -3773,18 +3866,21 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E101" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>5846</t>
         </is>
+      </c>
+      <c r="H101" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="102">
@@ -3804,18 +3900,21 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E102" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>11586</t>
         </is>
+      </c>
+      <c r="H102" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="103">
@@ -3866,7 +3965,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E104" t="n">
         <v>31</v>
@@ -3897,7 +3996,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E105" t="n">
         <v>33</v>
@@ -3928,7 +4027,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E106" t="n">
         <v>19</v>
@@ -3962,7 +4061,7 @@
         <v>101</v>
       </c>
       <c r="E107" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -4052,18 +4151,21 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="E110" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>5947</t>
         </is>
+      </c>
+      <c r="H110" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="111">
@@ -4083,10 +4185,10 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="E111" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -4117,7 +4219,7 @@
         <v>105</v>
       </c>
       <c r="E112" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -4179,7 +4281,7 @@
         <v>107</v>
       </c>
       <c r="E114" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -4272,7 +4374,7 @@
         <v>110</v>
       </c>
       <c r="E117" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -4334,7 +4436,7 @@
         <v>112</v>
       </c>
       <c r="E119" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -4458,7 +4560,7 @@
         <v>117</v>
       </c>
       <c r="E123" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -4520,7 +4622,7 @@
         <v>120</v>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -4582,7 +4684,7 @@
         <v>121</v>
       </c>
       <c r="E127" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -4644,7 +4746,7 @@
         <v>123</v>
       </c>
       <c r="E129" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -4675,7 +4777,7 @@
         <v>124</v>
       </c>
       <c r="E130" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -4703,18 +4805,21 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="E131" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>12533</t>
         </is>
+      </c>
+      <c r="H131" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="132">
@@ -4737,7 +4842,7 @@
         <v>126</v>
       </c>
       <c r="E132" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4768,7 +4873,7 @@
         <v>127</v>
       </c>
       <c r="E133" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -4830,7 +4935,7 @@
         <v>129</v>
       </c>
       <c r="E135" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -4861,15 +4966,18 @@
         <v>130</v>
       </c>
       <c r="E136" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
           <t>9756</t>
         </is>
+      </c>
+      <c r="H136" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="137">
@@ -4889,10 +4997,10 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>131</v>
+        <v>999</v>
       </c>
       <c r="E137" t="n">
-        <v>46</v>
+        <v>999</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4985,7 +5093,7 @@
         <v>134</v>
       </c>
       <c r="E140" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -5013,10 +5121,10 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="E141" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -5295,7 +5403,7 @@
         <v>148</v>
       </c>
       <c r="E150" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -5419,7 +5527,7 @@
         <v>153</v>
       </c>
       <c r="E154" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -5571,7 +5679,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="E159" t="n">
         <v>54</v>
@@ -5636,7 +5744,7 @@
         <v>162</v>
       </c>
       <c r="E161" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -5881,10 +5989,10 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>170</v>
+        <v>999</v>
       </c>
       <c r="E169" t="n">
-        <v>61</v>
+        <v>999</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -6687,7 +6795,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>198</v>
+        <v>104</v>
       </c>
       <c r="E195" t="n">
         <v>70</v>
@@ -6935,7 +7043,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>206</v>
+        <v>100</v>
       </c>
       <c r="E203" t="n">
         <v>74</v>
@@ -7338,7 +7446,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>219</v>
+        <v>100</v>
       </c>
       <c r="E216" t="n">
         <v>76</v>
@@ -7493,7 +7601,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>224</v>
+        <v>103</v>
       </c>
       <c r="E221" t="n">
         <v>84</v>
@@ -7648,18 +7756,21 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>229</v>
+        <v>100</v>
       </c>
       <c r="E226" t="n">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
           <t>10213</t>
         </is>
+      </c>
+      <c r="H226" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="227">
@@ -7958,7 +8069,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>239</v>
+        <v>100</v>
       </c>
       <c r="E236" t="n">
         <v>31</v>
@@ -8764,18 +8875,21 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>265</v>
+        <v>101</v>
       </c>
       <c r="E262" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
           <t>11834</t>
         </is>
+      </c>
+      <c r="H262" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="263">

--- a/players.xlsx
+++ b/players.xlsx
@@ -549,7 +549,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4">
@@ -583,7 +583,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
         <v>93</v>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
         <v>92</v>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
         <v>8</v>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
         <v>9</v>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
         <v>86</v>
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>93</v>
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F29" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30">
@@ -1461,13 +1461,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E32" t="n">
         <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33">
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
         <v>92</v>
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E34" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F34" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35">
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E35" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F35" t="n">
         <v>82</v>
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E36" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F36" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F38" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F39" t="n">
         <v>82</v>
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="E40" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F40" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41">
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E41" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F41" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42">
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E42" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F42" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E43" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F43" t="n">
         <v>79</v>
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E44" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F44" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F45" t="n">
         <v>80</v>
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F46" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47">
@@ -2036,13 +2036,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F47" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E48" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F48" t="n">
         <v>80</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
         <v>80</v>
@@ -2138,13 +2138,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E50" t="n">
         <v>19</v>
       </c>
       <c r="F50" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F51" t="n">
         <v>78</v>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E52" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F52" t="n">
         <v>77</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54">
@@ -2274,13 +2274,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E54" t="n">
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55">
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E55" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F55" t="n">
         <v>76</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F56" t="n">
         <v>76</v>
@@ -2379,7 +2379,7 @@
         <v>68</v>
       </c>
       <c r="E57" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F57" t="n">
         <v>71</v>
@@ -2410,13 +2410,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="E58" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F58" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E59" t="n">
         <v>3</v>
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F60" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
         <v>30</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E62" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F62" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63">
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F63" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         <v>61</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F64" t="n">
         <v>72</v>
@@ -2651,7 +2651,7 @@
         <v>62</v>
       </c>
       <c r="E65" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2682,7 +2682,7 @@
         <v>62</v>
       </c>
       <c r="E66" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F66" t="n">
         <v>72</v>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E68" t="n">
         <v>24</v>
       </c>
       <c r="F68" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="E69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70">
@@ -2815,13 +2815,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F70" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E71" t="n">
         <v>6</v>
@@ -2883,13 +2883,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E72" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F72" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>82</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E74" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F74" t="n">
         <v>70</v>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E76" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F76" t="n">
         <v>70</v>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E77" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F77" t="n">
         <v>69</v>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E78" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F78" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79">
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E79" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F79" t="n">
         <v>66</v>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E80" t="n">
         <v>8</v>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F81" t="n">
         <v>68</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E82" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F82" t="n">
         <v>68</v>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F83" t="n">
         <v>67</v>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -3325,13 +3325,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F85" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86">
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E86" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
         <v>66</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E87" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F87" t="n">
         <v>66</v>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E88" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F88" t="n">
         <v>67</v>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E89" t="n">
         <v>9</v>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E90" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E91" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F91" t="n">
         <v>66</v>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
         <v>80</v>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E93" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
         <v>66</v>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E94" t="n">
         <v>11</v>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E95" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
         <v>74</v>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E96" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E97" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F97" t="n">
         <v>64</v>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E98" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F98" t="n">
         <v>64</v>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E99" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F99" t="n">
         <v>62</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F100" t="n">
         <v>76</v>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E101" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F101" t="n">
         <v>62</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E102" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F102" t="n">
         <v>61</v>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E103" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E104" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E105" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E106" t="n">
         <v>19</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E107" t="n">
         <v>46</v>
@@ -4089,18 +4089,21 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="E108" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>7523</t>
         </is>
+      </c>
+      <c r="H108" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="109">
@@ -4120,10 +4123,10 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E109" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -4151,10 +4154,10 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E110" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F110" t="n">
         <v>69</v>
@@ -4185,10 +4188,10 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E111" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -4216,10 +4219,10 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E112" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -4247,10 +4250,10 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E113" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -4278,10 +4281,10 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E114" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -4309,10 +4312,10 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E115" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -4340,10 +4343,10 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E116" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -4371,7 +4374,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E117" t="n">
         <v>20</v>
@@ -4402,10 +4405,10 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E118" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -4433,10 +4436,10 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E119" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -4464,10 +4467,10 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E120" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -4495,10 +4498,10 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E121" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -4526,10 +4529,10 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E122" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -4557,10 +4560,10 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E123" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -4588,10 +4591,10 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E124" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -4619,10 +4622,10 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E125" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -4650,10 +4653,10 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E126" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -4681,10 +4684,10 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E127" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -4712,10 +4715,10 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E128" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -4743,10 +4746,10 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E129" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -4774,10 +4777,10 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E130" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -4805,10 +4808,10 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E131" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F131" t="n">
         <v>63</v>
@@ -4839,10 +4842,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E132" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4870,10 +4873,10 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E133" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -4901,10 +4904,10 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E134" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -4932,10 +4935,10 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E135" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -4963,10 +4966,10 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E136" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F136" t="n">
         <v>60</v>
@@ -5000,7 +5003,7 @@
         <v>999</v>
       </c>
       <c r="E137" t="n">
-        <v>999</v>
+        <v>416</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -5028,10 +5031,10 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E138" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -5059,10 +5062,10 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E139" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -5090,10 +5093,10 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E140" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -5121,10 +5124,10 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E141" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -5152,10 +5155,10 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E142" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -5183,10 +5186,10 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E143" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -5214,10 +5217,10 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E144" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -5245,10 +5248,10 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E145" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -5276,10 +5279,10 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E146" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -5307,10 +5310,10 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E147" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -5338,10 +5341,10 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E148" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -5369,10 +5372,10 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E149" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -5400,10 +5403,10 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E150" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -5431,10 +5434,10 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E151" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -5462,10 +5465,10 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E152" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -5493,10 +5496,10 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E153" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -5524,10 +5527,10 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E154" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -5555,7 +5558,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E155" t="n">
         <v>22</v>
@@ -5586,10 +5589,10 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E156" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -5617,10 +5620,10 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E157" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -5648,10 +5651,10 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E158" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -5679,18 +5682,21 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E159" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
           <t>4035</t>
         </is>
+      </c>
+      <c r="H159" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="160">
@@ -5710,10 +5716,10 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E160" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -5741,10 +5747,10 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E161" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -5772,10 +5778,10 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E162" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -5803,10 +5809,10 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E163" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -5834,10 +5840,10 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E164" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -5865,10 +5871,10 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E165" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -5896,10 +5902,10 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E166" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -5927,7 +5933,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E167" t="n">
         <v>23</v>
@@ -5958,10 +5964,10 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E168" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -5992,7 +5998,7 @@
         <v>999</v>
       </c>
       <c r="E169" t="n">
-        <v>999</v>
+        <v>417</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -6020,10 +6026,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E170" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -6051,7 +6057,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E171" t="n">
         <v>24</v>
@@ -6082,10 +6088,10 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E172" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -6113,10 +6119,10 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E173" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -6144,10 +6150,10 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E174" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -6175,7 +6181,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E175" t="n">
         <v>25</v>
@@ -6206,10 +6212,10 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E176" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
@@ -6237,10 +6243,10 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E177" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -6268,7 +6274,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E178" t="n">
         <v>26</v>
@@ -6299,7 +6305,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E179" t="n">
         <v>27</v>
@@ -6330,7 +6336,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E180" t="n">
         <v>28</v>
@@ -6361,7 +6367,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E181" t="n">
         <v>29</v>
@@ -6392,10 +6398,10 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E182" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -6423,7 +6429,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E183" t="n">
         <v>30</v>
@@ -6454,7 +6460,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E184" t="n">
         <v>31</v>
@@ -6485,10 +6491,10 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E185" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
@@ -6516,10 +6522,10 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E186" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -6547,10 +6553,10 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E187" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -6578,7 +6584,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E188" t="n">
         <v>32</v>
@@ -6609,10 +6615,10 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E189" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -6640,10 +6646,10 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E190" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
@@ -6671,10 +6677,10 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E191" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -6702,10 +6708,10 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E192" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -6733,10 +6739,10 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E193" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -6764,7 +6770,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E194" t="n">
         <v>33</v>
@@ -6795,10 +6801,10 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E195" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
@@ -6826,10 +6832,10 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E196" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
@@ -6857,10 +6863,10 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E197" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -6888,10 +6894,10 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E198" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -6919,10 +6925,10 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E199" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
@@ -6950,10 +6956,10 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E200" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
@@ -6981,10 +6987,10 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E201" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F201" t="n">
         <v>0</v>
@@ -7012,18 +7018,21 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="E202" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
           <t>11435</t>
         </is>
+      </c>
+      <c r="H202" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="203">
@@ -7043,10 +7052,10 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E203" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -7446,10 +7455,10 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E216" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
@@ -7511,7 +7520,7 @@
         <v>221</v>
       </c>
       <c r="E218" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -7542,7 +7551,7 @@
         <v>222</v>
       </c>
       <c r="E219" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
@@ -7601,10 +7610,10 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E221" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
@@ -7635,7 +7644,7 @@
         <v>225</v>
       </c>
       <c r="E222" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
@@ -7697,7 +7706,7 @@
         <v>227</v>
       </c>
       <c r="E224" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
@@ -7728,7 +7737,7 @@
         <v>228</v>
       </c>
       <c r="E225" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
@@ -7756,10 +7765,10 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E226" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F226" t="n">
         <v>61</v>
@@ -7793,7 +7802,7 @@
         <v>230</v>
       </c>
       <c r="E227" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -7824,7 +7833,7 @@
         <v>231</v>
       </c>
       <c r="E228" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
@@ -7855,7 +7864,7 @@
         <v>232</v>
       </c>
       <c r="E229" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F229" t="n">
         <v>0</v>
@@ -7886,7 +7895,7 @@
         <v>233</v>
       </c>
       <c r="E230" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F230" t="n">
         <v>0</v>
@@ -7917,7 +7926,7 @@
         <v>234</v>
       </c>
       <c r="E231" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
@@ -7948,7 +7957,7 @@
         <v>235</v>
       </c>
       <c r="E232" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
@@ -7979,7 +7988,7 @@
         <v>236</v>
       </c>
       <c r="E233" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F233" t="n">
         <v>0</v>
@@ -8010,7 +8019,7 @@
         <v>237</v>
       </c>
       <c r="E234" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
@@ -8041,7 +8050,7 @@
         <v>238</v>
       </c>
       <c r="E235" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -8069,10 +8078,10 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E236" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -8103,7 +8112,7 @@
         <v>240</v>
       </c>
       <c r="E237" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
@@ -8134,7 +8143,7 @@
         <v>241</v>
       </c>
       <c r="E238" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -8165,7 +8174,7 @@
         <v>242</v>
       </c>
       <c r="E239" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -8196,7 +8205,7 @@
         <v>243</v>
       </c>
       <c r="E240" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -8227,7 +8236,7 @@
         <v>244</v>
       </c>
       <c r="E241" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F241" t="n">
         <v>0</v>
@@ -8258,7 +8267,7 @@
         <v>245</v>
       </c>
       <c r="E242" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F242" t="n">
         <v>0</v>
@@ -8289,7 +8298,7 @@
         <v>246</v>
       </c>
       <c r="E243" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F243" t="n">
         <v>0</v>
@@ -8320,7 +8329,7 @@
         <v>247</v>
       </c>
       <c r="E244" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
@@ -8351,7 +8360,7 @@
         <v>248</v>
       </c>
       <c r="E245" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F245" t="n">
         <v>0</v>
@@ -8382,7 +8391,7 @@
         <v>249</v>
       </c>
       <c r="E246" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
@@ -8413,7 +8422,7 @@
         <v>250</v>
       </c>
       <c r="E247" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
@@ -8444,7 +8453,7 @@
         <v>251</v>
       </c>
       <c r="E248" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F248" t="n">
         <v>0</v>
@@ -8475,7 +8484,7 @@
         <v>252</v>
       </c>
       <c r="E249" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F249" t="n">
         <v>0</v>
@@ -8506,7 +8515,7 @@
         <v>253</v>
       </c>
       <c r="E250" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F250" t="n">
         <v>0</v>
@@ -8537,7 +8546,7 @@
         <v>254</v>
       </c>
       <c r="E251" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F251" t="n">
         <v>0</v>
@@ -8568,7 +8577,7 @@
         <v>255</v>
       </c>
       <c r="E252" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F252" t="n">
         <v>0</v>
@@ -8599,7 +8608,7 @@
         <v>256</v>
       </c>
       <c r="E253" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F253" t="n">
         <v>0</v>
@@ -8630,7 +8639,7 @@
         <v>257</v>
       </c>
       <c r="E254" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F254" t="n">
         <v>0</v>
@@ -8661,7 +8670,7 @@
         <v>258</v>
       </c>
       <c r="E255" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -8692,7 +8701,7 @@
         <v>259</v>
       </c>
       <c r="E256" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F256" t="n">
         <v>0</v>
@@ -8723,7 +8732,7 @@
         <v>260</v>
       </c>
       <c r="E257" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F257" t="n">
         <v>0</v>
@@ -8754,7 +8763,7 @@
         <v>261</v>
       </c>
       <c r="E258" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F258" t="n">
         <v>0</v>
@@ -8785,7 +8794,7 @@
         <v>262</v>
       </c>
       <c r="E259" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
@@ -8816,7 +8825,7 @@
         <v>263</v>
       </c>
       <c r="E260" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
@@ -8847,7 +8856,7 @@
         <v>264</v>
       </c>
       <c r="E261" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
@@ -8875,10 +8884,10 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E262" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F262" t="n">
         <v>60</v>
@@ -8912,7 +8921,7 @@
         <v>266</v>
       </c>
       <c r="E263" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
@@ -8943,7 +8952,7 @@
         <v>267</v>
       </c>
       <c r="E264" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
@@ -9005,7 +9014,7 @@
         <v>269</v>
       </c>
       <c r="E266" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F266" t="n">
         <v>0</v>
@@ -9036,7 +9045,7 @@
         <v>270</v>
       </c>
       <c r="E267" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F267" t="n">
         <v>0</v>
@@ -9067,7 +9076,7 @@
         <v>271</v>
       </c>
       <c r="E268" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F268" t="n">
         <v>0</v>
@@ -9160,7 +9169,7 @@
         <v>274</v>
       </c>
       <c r="E271" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F271" t="n">
         <v>0</v>
@@ -9191,7 +9200,7 @@
         <v>275</v>
       </c>
       <c r="E272" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F272" t="n">
         <v>0</v>
@@ -9253,7 +9262,7 @@
         <v>277</v>
       </c>
       <c r="E274" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F274" t="n">
         <v>0</v>
@@ -9284,7 +9293,7 @@
         <v>278</v>
       </c>
       <c r="E275" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F275" t="n">
         <v>0</v>
@@ -9315,7 +9324,7 @@
         <v>279</v>
       </c>
       <c r="E276" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F276" t="n">
         <v>0</v>
@@ -9346,7 +9355,7 @@
         <v>280</v>
       </c>
       <c r="E277" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F277" t="n">
         <v>0</v>
@@ -9377,7 +9386,7 @@
         <v>281</v>
       </c>
       <c r="E278" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F278" t="n">
         <v>0</v>
@@ -9408,7 +9417,7 @@
         <v>282</v>
       </c>
       <c r="E279" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
@@ -9439,7 +9448,7 @@
         <v>283</v>
       </c>
       <c r="E280" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F280" t="n">
         <v>0</v>
@@ -9470,7 +9479,7 @@
         <v>284</v>
       </c>
       <c r="E281" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F281" t="n">
         <v>0</v>
@@ -9501,7 +9510,7 @@
         <v>285</v>
       </c>
       <c r="E282" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F282" t="n">
         <v>0</v>
@@ -9594,7 +9603,7 @@
         <v>288</v>
       </c>
       <c r="E285" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F285" t="n">
         <v>0</v>
@@ -9625,7 +9634,7 @@
         <v>289</v>
       </c>
       <c r="E286" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
@@ -9656,7 +9665,7 @@
         <v>290</v>
       </c>
       <c r="E287" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F287" t="n">
         <v>0</v>
@@ -9687,7 +9696,7 @@
         <v>291</v>
       </c>
       <c r="E288" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
@@ -9718,7 +9727,7 @@
         <v>292</v>
       </c>
       <c r="E289" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
@@ -9749,7 +9758,7 @@
         <v>293</v>
       </c>
       <c r="E290" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F290" t="n">
         <v>0</v>
@@ -9780,7 +9789,7 @@
         <v>294</v>
       </c>
       <c r="E291" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F291" t="n">
         <v>0</v>
@@ -9811,7 +9820,7 @@
         <v>295</v>
       </c>
       <c r="E292" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F292" t="n">
         <v>0</v>
@@ -9842,7 +9851,7 @@
         <v>296</v>
       </c>
       <c r="E293" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F293" t="n">
         <v>0</v>
@@ -9873,7 +9882,7 @@
         <v>297</v>
       </c>
       <c r="E294" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
@@ -9904,7 +9913,7 @@
         <v>298</v>
       </c>
       <c r="E295" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F295" t="n">
         <v>0</v>
@@ -9935,7 +9944,7 @@
         <v>299</v>
       </c>
       <c r="E296" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F296" t="n">
         <v>0</v>
@@ -9966,7 +9975,7 @@
         <v>300</v>
       </c>
       <c r="E297" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F297" t="n">
         <v>0</v>
@@ -9997,7 +10006,7 @@
         <v>301</v>
       </c>
       <c r="E298" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F298" t="n">
         <v>0</v>
@@ -10059,7 +10068,7 @@
         <v>303</v>
       </c>
       <c r="E300" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F300" t="n">
         <v>0</v>
@@ -10090,7 +10099,7 @@
         <v>304</v>
       </c>
       <c r="E301" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F301" t="n">
         <v>0</v>
@@ -10121,7 +10130,7 @@
         <v>305</v>
       </c>
       <c r="E302" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F302" t="n">
         <v>0</v>
@@ -10152,7 +10161,7 @@
         <v>306</v>
       </c>
       <c r="E303" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F303" t="n">
         <v>0</v>
@@ -10214,7 +10223,7 @@
         <v>308</v>
       </c>
       <c r="E305" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F305" t="n">
         <v>0</v>
@@ -10245,7 +10254,7 @@
         <v>309</v>
       </c>
       <c r="E306" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F306" t="n">
         <v>0</v>
@@ -10276,7 +10285,7 @@
         <v>310</v>
       </c>
       <c r="E307" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F307" t="n">
         <v>0</v>
@@ -10338,7 +10347,7 @@
         <v>312</v>
       </c>
       <c r="E309" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F309" t="n">
         <v>0</v>
@@ -10369,7 +10378,7 @@
         <v>313</v>
       </c>
       <c r="E310" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F310" t="n">
         <v>0</v>
@@ -10400,7 +10409,7 @@
         <v>314</v>
       </c>
       <c r="E311" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F311" t="n">
         <v>0</v>
@@ -10431,7 +10440,7 @@
         <v>315</v>
       </c>
       <c r="E312" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F312" t="n">
         <v>0</v>
@@ -10462,7 +10471,7 @@
         <v>316</v>
       </c>
       <c r="E313" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F313" t="n">
         <v>0</v>
@@ -10493,7 +10502,7 @@
         <v>317</v>
       </c>
       <c r="E314" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
@@ -10555,7 +10564,7 @@
         <v>319</v>
       </c>
       <c r="E316" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F316" t="n">
         <v>0</v>
@@ -10617,7 +10626,7 @@
         <v>321</v>
       </c>
       <c r="E318" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F318" t="n">
         <v>0</v>
@@ -10648,7 +10657,7 @@
         <v>322</v>
       </c>
       <c r="E319" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F319" t="n">
         <v>0</v>
@@ -10679,7 +10688,7 @@
         <v>323</v>
       </c>
       <c r="E320" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F320" t="n">
         <v>0</v>
@@ -10741,7 +10750,7 @@
         <v>325</v>
       </c>
       <c r="E322" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F322" t="n">
         <v>0</v>
@@ -10772,7 +10781,7 @@
         <v>326</v>
       </c>
       <c r="E323" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F323" t="n">
         <v>0</v>
@@ -10803,7 +10812,7 @@
         <v>327</v>
       </c>
       <c r="E324" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F324" t="n">
         <v>0</v>
@@ -10834,7 +10843,7 @@
         <v>328</v>
       </c>
       <c r="E325" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F325" t="n">
         <v>0</v>
@@ -10896,7 +10905,7 @@
         <v>330</v>
       </c>
       <c r="E327" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F327" t="n">
         <v>0</v>
@@ -10927,7 +10936,7 @@
         <v>331</v>
       </c>
       <c r="E328" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F328" t="n">
         <v>0</v>
@@ -10958,7 +10967,7 @@
         <v>332</v>
       </c>
       <c r="E329" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F329" t="n">
         <v>0</v>
@@ -11051,7 +11060,7 @@
         <v>335</v>
       </c>
       <c r="E332" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F332" t="n">
         <v>0</v>
@@ -11082,7 +11091,7 @@
         <v>336</v>
       </c>
       <c r="E333" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F333" t="n">
         <v>0</v>
@@ -11113,7 +11122,7 @@
         <v>337</v>
       </c>
       <c r="E334" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F334" t="n">
         <v>0</v>
@@ -11144,7 +11153,7 @@
         <v>338</v>
       </c>
       <c r="E335" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
@@ -11175,7 +11184,7 @@
         <v>339</v>
       </c>
       <c r="E336" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
@@ -11206,7 +11215,7 @@
         <v>340</v>
       </c>
       <c r="E337" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F337" t="n">
         <v>0</v>
@@ -11237,7 +11246,7 @@
         <v>341</v>
       </c>
       <c r="E338" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F338" t="n">
         <v>0</v>
@@ -11268,7 +11277,7 @@
         <v>342</v>
       </c>
       <c r="E339" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F339" t="n">
         <v>0</v>
@@ -11299,7 +11308,7 @@
         <v>343</v>
       </c>
       <c r="E340" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F340" t="n">
         <v>0</v>
@@ -11330,7 +11339,7 @@
         <v>344</v>
       </c>
       <c r="E341" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F341" t="n">
         <v>0</v>
@@ -11361,7 +11370,7 @@
         <v>345</v>
       </c>
       <c r="E342" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
@@ -11423,7 +11432,7 @@
         <v>347</v>
       </c>
       <c r="E344" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F344" t="n">
         <v>0</v>
@@ -11485,7 +11494,7 @@
         <v>349</v>
       </c>
       <c r="E346" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F346" t="n">
         <v>0</v>
@@ -11516,7 +11525,7 @@
         <v>350</v>
       </c>
       <c r="E347" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F347" t="n">
         <v>0</v>
@@ -11547,7 +11556,7 @@
         <v>351</v>
       </c>
       <c r="E348" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F348" t="n">
         <v>0</v>
@@ -11578,7 +11587,7 @@
         <v>352</v>
       </c>
       <c r="E349" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F349" t="n">
         <v>0</v>
@@ -11609,7 +11618,7 @@
         <v>353</v>
       </c>
       <c r="E350" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
@@ -11640,7 +11649,7 @@
         <v>354</v>
       </c>
       <c r="E351" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F351" t="n">
         <v>0</v>
@@ -11702,7 +11711,7 @@
         <v>356</v>
       </c>
       <c r="E353" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F353" t="n">
         <v>0</v>
@@ -11733,7 +11742,7 @@
         <v>357</v>
       </c>
       <c r="E354" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F354" t="n">
         <v>0</v>
@@ -11764,7 +11773,7 @@
         <v>358</v>
       </c>
       <c r="E355" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F355" t="n">
         <v>0</v>
@@ -11795,7 +11804,7 @@
         <v>359</v>
       </c>
       <c r="E356" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F356" t="n">
         <v>0</v>
@@ -11857,7 +11866,7 @@
         <v>361</v>
       </c>
       <c r="E358" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F358" t="n">
         <v>0</v>
@@ -11888,7 +11897,7 @@
         <v>362</v>
       </c>
       <c r="E359" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F359" t="n">
         <v>0</v>
@@ -11919,7 +11928,7 @@
         <v>363</v>
       </c>
       <c r="E360" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F360" t="n">
         <v>0</v>
@@ -11950,7 +11959,7 @@
         <v>364</v>
       </c>
       <c r="E361" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F361" t="n">
         <v>0</v>
@@ -11981,7 +11990,7 @@
         <v>365</v>
       </c>
       <c r="E362" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F362" t="n">
         <v>0</v>
@@ -12012,7 +12021,7 @@
         <v>366</v>
       </c>
       <c r="E363" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F363" t="n">
         <v>0</v>
@@ -12043,7 +12052,7 @@
         <v>367</v>
       </c>
       <c r="E364" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
@@ -12074,7 +12083,7 @@
         <v>368</v>
       </c>
       <c r="E365" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F365" t="n">
         <v>0</v>
@@ -12136,7 +12145,7 @@
         <v>370</v>
       </c>
       <c r="E367" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F367" t="n">
         <v>0</v>
@@ -12167,7 +12176,7 @@
         <v>371</v>
       </c>
       <c r="E368" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F368" t="n">
         <v>0</v>
@@ -12198,7 +12207,7 @@
         <v>372</v>
       </c>
       <c r="E369" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F369" t="n">
         <v>0</v>
@@ -12229,7 +12238,7 @@
         <v>373</v>
       </c>
       <c r="E370" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F370" t="n">
         <v>0</v>
@@ -12260,7 +12269,7 @@
         <v>374</v>
       </c>
       <c r="E371" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F371" t="n">
         <v>0</v>
@@ -12291,7 +12300,7 @@
         <v>375</v>
       </c>
       <c r="E372" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F372" t="n">
         <v>0</v>
@@ -12322,7 +12331,7 @@
         <v>376</v>
       </c>
       <c r="E373" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F373" t="n">
         <v>0</v>
@@ -12353,7 +12362,7 @@
         <v>377</v>
       </c>
       <c r="E374" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F374" t="n">
         <v>0</v>
@@ -12384,7 +12393,7 @@
         <v>378</v>
       </c>
       <c r="E375" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F375" t="n">
         <v>0</v>
@@ -12415,7 +12424,7 @@
         <v>379</v>
       </c>
       <c r="E376" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F376" t="n">
         <v>0</v>
@@ -12477,7 +12486,7 @@
         <v>381</v>
       </c>
       <c r="E378" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F378" t="n">
         <v>0</v>
@@ -12508,7 +12517,7 @@
         <v>382</v>
       </c>
       <c r="E379" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F379" t="n">
         <v>0</v>
@@ -12539,7 +12548,7 @@
         <v>383</v>
       </c>
       <c r="E380" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F380" t="n">
         <v>0</v>
@@ -12601,7 +12610,7 @@
         <v>385</v>
       </c>
       <c r="E382" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F382" t="n">
         <v>0</v>
@@ -12632,7 +12641,7 @@
         <v>386</v>
       </c>
       <c r="E383" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F383" t="n">
         <v>0</v>
@@ -12663,7 +12672,7 @@
         <v>387</v>
       </c>
       <c r="E384" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F384" t="n">
         <v>0</v>
@@ -12725,7 +12734,7 @@
         <v>389</v>
       </c>
       <c r="E386" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F386" t="n">
         <v>0</v>
@@ -12756,7 +12765,7 @@
         <v>390</v>
       </c>
       <c r="E387" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F387" t="n">
         <v>0</v>
@@ -12787,7 +12796,7 @@
         <v>391</v>
       </c>
       <c r="E388" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F388" t="n">
         <v>0</v>
@@ -12818,7 +12827,7 @@
         <v>392</v>
       </c>
       <c r="E389" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F389" t="n">
         <v>0</v>
@@ -12880,7 +12889,7 @@
         <v>394</v>
       </c>
       <c r="E391" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F391" t="n">
         <v>0</v>
@@ -12911,7 +12920,7 @@
         <v>395</v>
       </c>
       <c r="E392" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F392" t="n">
         <v>0</v>
@@ -12942,7 +12951,7 @@
         <v>396</v>
       </c>
       <c r="E393" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F393" t="n">
         <v>0</v>
@@ -12973,7 +12982,7 @@
         <v>397</v>
       </c>
       <c r="E394" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F394" t="n">
         <v>0</v>
@@ -13004,7 +13013,7 @@
         <v>398</v>
       </c>
       <c r="E395" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F395" t="n">
         <v>0</v>
@@ -13035,7 +13044,7 @@
         <v>399</v>
       </c>
       <c r="E396" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F396" t="n">
         <v>0</v>
@@ -13066,7 +13075,7 @@
         <v>400</v>
       </c>
       <c r="E397" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F397" t="n">
         <v>0</v>
@@ -13097,7 +13106,7 @@
         <v>401</v>
       </c>
       <c r="E398" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F398" t="n">
         <v>0</v>
@@ -13128,7 +13137,7 @@
         <v>402</v>
       </c>
       <c r="E399" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F399" t="n">
         <v>0</v>
@@ -13159,7 +13168,7 @@
         <v>403</v>
       </c>
       <c r="E400" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F400" t="n">
         <v>0</v>
@@ -13190,7 +13199,7 @@
         <v>404</v>
       </c>
       <c r="E401" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F401" t="n">
         <v>0</v>
@@ -13221,7 +13230,7 @@
         <v>405</v>
       </c>
       <c r="E402" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F402" t="n">
         <v>0</v>
@@ -13252,7 +13261,7 @@
         <v>406</v>
       </c>
       <c r="E403" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F403" t="n">
         <v>0</v>
@@ -13283,7 +13292,7 @@
         <v>407</v>
       </c>
       <c r="E404" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F404" t="n">
         <v>0</v>
@@ -13376,7 +13385,7 @@
         <v>410</v>
       </c>
       <c r="E407" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F407" t="n">
         <v>0</v>
@@ -13407,7 +13416,7 @@
         <v>411</v>
       </c>
       <c r="E408" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F408" t="n">
         <v>0</v>
@@ -13438,7 +13447,7 @@
         <v>412</v>
       </c>
       <c r="E409" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F409" t="n">
         <v>0</v>
@@ -13469,7 +13478,7 @@
         <v>413</v>
       </c>
       <c r="E410" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F410" t="n">
         <v>0</v>
@@ -13500,7 +13509,7 @@
         <v>414</v>
       </c>
       <c r="E411" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F411" t="n">
         <v>0</v>
@@ -13531,7 +13540,7 @@
         <v>415</v>
       </c>
       <c r="E412" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F412" t="n">
         <v>0</v>
@@ -13562,7 +13571,7 @@
         <v>416</v>
       </c>
       <c r="E413" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F413" t="n">
         <v>0</v>
@@ -13593,7 +13602,7 @@
         <v>417</v>
       </c>
       <c r="E414" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F414" t="n">
         <v>0</v>
@@ -13624,7 +13633,7 @@
         <v>418</v>
       </c>
       <c r="E415" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F415" t="n">
         <v>0</v>
@@ -13655,7 +13664,7 @@
         <v>419</v>
       </c>
       <c r="E416" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F416" t="n">
         <v>0</v>
@@ -13717,7 +13726,7 @@
         <v>421</v>
       </c>
       <c r="E418" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F418" t="n">
         <v>0</v>
@@ -13779,7 +13788,7 @@
         <v>423</v>
       </c>
       <c r="E420" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F420" t="n">
         <v>0</v>
@@ -13810,7 +13819,7 @@
         <v>424</v>
       </c>
       <c r="E421" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F421" t="n">
         <v>0</v>
@@ -13841,7 +13850,7 @@
         <v>425</v>
       </c>
       <c r="E422" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F422" t="n">
         <v>0</v>
@@ -13872,7 +13881,7 @@
         <v>426</v>
       </c>
       <c r="E423" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F423" t="n">
         <v>0</v>
@@ -13903,7 +13912,7 @@
         <v>427</v>
       </c>
       <c r="E424" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F424" t="n">
         <v>0</v>
@@ -13965,7 +13974,7 @@
         <v>429</v>
       </c>
       <c r="E426" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F426" t="n">
         <v>0</v>
@@ -13996,7 +14005,7 @@
         <v>430</v>
       </c>
       <c r="E427" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F427" t="n">
         <v>0</v>
@@ -14027,7 +14036,7 @@
         <v>431</v>
       </c>
       <c r="E428" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F428" t="n">
         <v>0</v>
@@ -14058,7 +14067,7 @@
         <v>432</v>
       </c>
       <c r="E429" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F429" t="n">
         <v>0</v>
@@ -14089,7 +14098,7 @@
         <v>433</v>
       </c>
       <c r="E430" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F430" t="n">
         <v>0</v>
@@ -14120,7 +14129,7 @@
         <v>434</v>
       </c>
       <c r="E431" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F431" t="n">
         <v>0</v>
@@ -14182,7 +14191,7 @@
         <v>436</v>
       </c>
       <c r="E433" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F433" t="n">
         <v>0</v>
@@ -14244,7 +14253,7 @@
         <v>438</v>
       </c>
       <c r="E435" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F435" t="n">
         <v>0</v>
@@ -14275,7 +14284,7 @@
         <v>439</v>
       </c>
       <c r="E436" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F436" t="n">
         <v>0</v>
@@ -14306,7 +14315,7 @@
         <v>440</v>
       </c>
       <c r="E437" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F437" t="n">
         <v>0</v>
@@ -14368,7 +14377,7 @@
         <v>442</v>
       </c>
       <c r="E439" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F439" t="n">
         <v>0</v>
@@ -14430,7 +14439,7 @@
         <v>444</v>
       </c>
       <c r="E441" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F441" t="n">
         <v>0</v>
@@ -14461,7 +14470,7 @@
         <v>445</v>
       </c>
       <c r="E442" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F442" t="n">
         <v>0</v>
@@ -14492,7 +14501,7 @@
         <v>446</v>
       </c>
       <c r="E443" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F443" t="n">
         <v>0</v>
@@ -14523,7 +14532,7 @@
         <v>447</v>
       </c>
       <c r="E444" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F444" t="n">
         <v>0</v>
@@ -14554,7 +14563,7 @@
         <v>448</v>
       </c>
       <c r="E445" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F445" t="n">
         <v>0</v>
@@ -14585,7 +14594,7 @@
         <v>449</v>
       </c>
       <c r="E446" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F446" t="n">
         <v>0</v>
@@ -14647,7 +14656,7 @@
         <v>451</v>
       </c>
       <c r="E448" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F448" t="n">
         <v>0</v>
@@ -14678,7 +14687,7 @@
         <v>452</v>
       </c>
       <c r="E449" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F449" t="n">
         <v>0</v>
@@ -14709,7 +14718,7 @@
         <v>453</v>
       </c>
       <c r="E450" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F450" t="n">
         <v>0</v>
@@ -14740,7 +14749,7 @@
         <v>454</v>
       </c>
       <c r="E451" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F451" t="n">
         <v>0</v>
@@ -14771,7 +14780,7 @@
         <v>455</v>
       </c>
       <c r="E452" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F452" t="n">
         <v>0</v>
@@ -14802,7 +14811,7 @@
         <v>456</v>
       </c>
       <c r="E453" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F453" t="n">
         <v>0</v>
@@ -14833,7 +14842,7 @@
         <v>457</v>
       </c>
       <c r="E454" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F454" t="n">
         <v>0</v>
@@ -14864,7 +14873,7 @@
         <v>458</v>
       </c>
       <c r="E455" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F455" t="n">
         <v>0</v>
@@ -14895,7 +14904,7 @@
         <v>459</v>
       </c>
       <c r="E456" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F456" t="n">
         <v>0</v>
@@ -14988,7 +14997,7 @@
         <v>462</v>
       </c>
       <c r="E459" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F459" t="n">
         <v>0</v>
@@ -15081,7 +15090,7 @@
         <v>465</v>
       </c>
       <c r="E462" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F462" t="n">
         <v>0</v>
@@ -15112,7 +15121,7 @@
         <v>466</v>
       </c>
       <c r="E463" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F463" t="n">
         <v>0</v>
@@ -15236,7 +15245,7 @@
         <v>470</v>
       </c>
       <c r="E467" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F467" t="n">
         <v>0</v>
@@ -15267,7 +15276,7 @@
         <v>471</v>
       </c>
       <c r="E468" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F468" t="n">
         <v>0</v>
@@ -15298,7 +15307,7 @@
         <v>472</v>
       </c>
       <c r="E469" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F469" t="n">
         <v>0</v>
@@ -15329,7 +15338,7 @@
         <v>473</v>
       </c>
       <c r="E470" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F470" t="n">
         <v>0</v>
@@ -15360,7 +15369,7 @@
         <v>474</v>
       </c>
       <c r="E471" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F471" t="n">
         <v>0</v>
@@ -15391,7 +15400,7 @@
         <v>475</v>
       </c>
       <c r="E472" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F472" t="n">
         <v>0</v>
@@ -15422,7 +15431,7 @@
         <v>476</v>
       </c>
       <c r="E473" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F473" t="n">
         <v>0</v>
@@ -15515,7 +15524,7 @@
         <v>479</v>
       </c>
       <c r="E476" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F476" t="n">
         <v>0</v>
@@ -15577,7 +15586,7 @@
         <v>481</v>
       </c>
       <c r="E478" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F478" t="n">
         <v>0</v>
@@ -15608,7 +15617,7 @@
         <v>482</v>
       </c>
       <c r="E479" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F479" t="n">
         <v>0</v>
@@ -15639,7 +15648,7 @@
         <v>483</v>
       </c>
       <c r="E480" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F480" t="n">
         <v>0</v>
@@ -15670,7 +15679,7 @@
         <v>484</v>
       </c>
       <c r="E481" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F481" t="n">
         <v>0</v>
@@ -15701,7 +15710,7 @@
         <v>485</v>
       </c>
       <c r="E482" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F482" t="n">
         <v>0</v>
@@ -15732,7 +15741,7 @@
         <v>486</v>
       </c>
       <c r="E483" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F483" t="n">
         <v>0</v>
@@ -15825,7 +15834,7 @@
         <v>489</v>
       </c>
       <c r="E486" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F486" t="n">
         <v>0</v>
@@ -15856,7 +15865,7 @@
         <v>490</v>
       </c>
       <c r="E487" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F487" t="n">
         <v>0</v>
@@ -15887,7 +15896,7 @@
         <v>491</v>
       </c>
       <c r="E488" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F488" t="n">
         <v>0</v>
@@ -15918,7 +15927,7 @@
         <v>492</v>
       </c>
       <c r="E489" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F489" t="n">
         <v>0</v>
@@ -15949,7 +15958,7 @@
         <v>493</v>
       </c>
       <c r="E490" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F490" t="n">
         <v>0</v>
@@ -15980,7 +15989,7 @@
         <v>494</v>
       </c>
       <c r="E491" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F491" t="n">
         <v>0</v>
@@ -16011,7 +16020,7 @@
         <v>495</v>
       </c>
       <c r="E492" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F492" t="n">
         <v>0</v>
@@ -16073,7 +16082,7 @@
         <v>497</v>
       </c>
       <c r="E494" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F494" t="n">
         <v>0</v>
@@ -16104,7 +16113,7 @@
         <v>498</v>
       </c>
       <c r="E495" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F495" t="n">
         <v>0</v>
@@ -16135,7 +16144,7 @@
         <v>499</v>
       </c>
       <c r="E496" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F496" t="n">
         <v>0</v>
@@ -16166,7 +16175,7 @@
         <v>500</v>
       </c>
       <c r="E497" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F497" t="n">
         <v>0</v>
@@ -16228,7 +16237,7 @@
         <v>502</v>
       </c>
       <c r="E499" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F499" t="n">
         <v>0</v>
@@ -16321,7 +16330,7 @@
         <v>505</v>
       </c>
       <c r="E502" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F502" t="n">
         <v>0</v>
@@ -16352,7 +16361,7 @@
         <v>506</v>
       </c>
       <c r="E503" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F503" t="n">
         <v>0</v>
@@ -16383,7 +16392,7 @@
         <v>507</v>
       </c>
       <c r="E504" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F504" t="n">
         <v>0</v>
@@ -16414,7 +16423,7 @@
         <v>508</v>
       </c>
       <c r="E505" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F505" t="n">
         <v>0</v>
@@ -16445,7 +16454,7 @@
         <v>509</v>
       </c>
       <c r="E506" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F506" t="n">
         <v>0</v>
@@ -16476,7 +16485,7 @@
         <v>510</v>
       </c>
       <c r="E507" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F507" t="n">
         <v>0</v>
@@ -16507,7 +16516,7 @@
         <v>511</v>
       </c>
       <c r="E508" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F508" t="n">
         <v>0</v>
@@ -16538,7 +16547,7 @@
         <v>512</v>
       </c>
       <c r="E509" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F509" t="n">
         <v>0</v>
@@ -16662,7 +16671,7 @@
         <v>516</v>
       </c>
       <c r="E513" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F513" t="n">
         <v>0</v>
@@ -16693,7 +16702,7 @@
         <v>517</v>
       </c>
       <c r="E514" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F514" t="n">
         <v>0</v>
@@ -16724,7 +16733,7 @@
         <v>518</v>
       </c>
       <c r="E515" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F515" t="n">
         <v>0</v>
@@ -16786,7 +16795,7 @@
         <v>520</v>
       </c>
       <c r="E517" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F517" t="n">
         <v>0</v>
@@ -16817,7 +16826,7 @@
         <v>521</v>
       </c>
       <c r="E518" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F518" t="n">
         <v>0</v>
@@ -16848,7 +16857,7 @@
         <v>522</v>
       </c>
       <c r="E519" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F519" t="n">
         <v>0</v>
@@ -16910,7 +16919,7 @@
         <v>524</v>
       </c>
       <c r="E521" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F521" t="n">
         <v>0</v>
@@ -16941,7 +16950,7 @@
         <v>525</v>
       </c>
       <c r="E522" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F522" t="n">
         <v>0</v>
@@ -16972,7 +16981,7 @@
         <v>526</v>
       </c>
       <c r="E523" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F523" t="n">
         <v>0</v>
@@ -17003,7 +17012,7 @@
         <v>527</v>
       </c>
       <c r="E524" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F524" t="n">
         <v>0</v>
@@ -17034,7 +17043,7 @@
         <v>528</v>
       </c>
       <c r="E525" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F525" t="n">
         <v>0</v>
@@ -17065,7 +17074,7 @@
         <v>529</v>
       </c>
       <c r="E526" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F526" t="n">
         <v>0</v>
@@ -17096,7 +17105,7 @@
         <v>530</v>
       </c>
       <c r="E527" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F527" t="n">
         <v>0</v>
@@ -17127,7 +17136,7 @@
         <v>531</v>
       </c>
       <c r="E528" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F528" t="n">
         <v>0</v>
@@ -17158,7 +17167,7 @@
         <v>532</v>
       </c>
       <c r="E529" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F529" t="n">
         <v>0</v>
@@ -17189,7 +17198,7 @@
         <v>533</v>
       </c>
       <c r="E530" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F530" t="n">
         <v>0</v>
@@ -17220,7 +17229,7 @@
         <v>534</v>
       </c>
       <c r="E531" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F531" t="n">
         <v>0</v>
@@ -17251,7 +17260,7 @@
         <v>535</v>
       </c>
       <c r="E532" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F532" t="n">
         <v>0</v>
@@ -17282,7 +17291,7 @@
         <v>536</v>
       </c>
       <c r="E533" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F533" t="n">
         <v>0</v>
@@ -17344,7 +17353,7 @@
         <v>538</v>
       </c>
       <c r="E535" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F535" t="n">
         <v>0</v>
@@ -17375,7 +17384,7 @@
         <v>539</v>
       </c>
       <c r="E536" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F536" t="n">
         <v>0</v>
@@ -17406,7 +17415,7 @@
         <v>540</v>
       </c>
       <c r="E537" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F537" t="n">
         <v>0</v>
@@ -17437,7 +17446,7 @@
         <v>541</v>
       </c>
       <c r="E538" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F538" t="n">
         <v>0</v>
@@ -17468,7 +17477,7 @@
         <v>542</v>
       </c>
       <c r="E539" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F539" t="n">
         <v>0</v>
@@ -17499,7 +17508,7 @@
         <v>543</v>
       </c>
       <c r="E540" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F540" t="n">
         <v>0</v>
@@ -17561,7 +17570,7 @@
         <v>545</v>
       </c>
       <c r="E542" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F542" t="n">
         <v>0</v>
@@ -17592,7 +17601,7 @@
         <v>546</v>
       </c>
       <c r="E543" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F543" t="n">
         <v>0</v>
@@ -17623,7 +17632,7 @@
         <v>547</v>
       </c>
       <c r="E544" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F544" t="n">
         <v>0</v>
@@ -17654,7 +17663,7 @@
         <v>548</v>
       </c>
       <c r="E545" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F545" t="n">
         <v>0</v>
@@ -17685,7 +17694,7 @@
         <v>549</v>
       </c>
       <c r="E546" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F546" t="n">
         <v>0</v>
@@ -17716,7 +17725,7 @@
         <v>550</v>
       </c>
       <c r="E547" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F547" t="n">
         <v>0</v>
@@ -17747,7 +17756,7 @@
         <v>551</v>
       </c>
       <c r="E548" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F548" t="n">
         <v>0</v>
@@ -17778,7 +17787,7 @@
         <v>552</v>
       </c>
       <c r="E549" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F549" t="n">
         <v>0</v>
@@ -17809,7 +17818,7 @@
         <v>553</v>
       </c>
       <c r="E550" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F550" t="n">
         <v>0</v>
@@ -17871,7 +17880,7 @@
         <v>555</v>
       </c>
       <c r="E552" t="n">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F552" t="n">
         <v>0</v>
@@ -17902,7 +17911,7 @@
         <v>556</v>
       </c>
       <c r="E553" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F553" t="n">
         <v>0</v>
@@ -17933,7 +17942,7 @@
         <v>557</v>
       </c>
       <c r="E554" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F554" t="n">
         <v>0</v>
@@ -17964,7 +17973,7 @@
         <v>558</v>
       </c>
       <c r="E555" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F555" t="n">
         <v>0</v>
@@ -17995,7 +18004,7 @@
         <v>559</v>
       </c>
       <c r="E556" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F556" t="n">
         <v>0</v>
@@ -18026,7 +18035,7 @@
         <v>560</v>
       </c>
       <c r="E557" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F557" t="n">
         <v>0</v>
@@ -18088,7 +18097,7 @@
         <v>562</v>
       </c>
       <c r="E559" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F559" t="n">
         <v>0</v>
@@ -18119,7 +18128,7 @@
         <v>563</v>
       </c>
       <c r="E560" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F560" t="n">
         <v>0</v>
@@ -18150,7 +18159,7 @@
         <v>564</v>
       </c>
       <c r="E561" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F561" t="n">
         <v>0</v>
@@ -18212,7 +18221,7 @@
         <v>566</v>
       </c>
       <c r="E563" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F563" t="n">
         <v>0</v>
@@ -18243,7 +18252,7 @@
         <v>567</v>
       </c>
       <c r="E564" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F564" t="n">
         <v>0</v>
@@ -18274,7 +18283,7 @@
         <v>568</v>
       </c>
       <c r="E565" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F565" t="n">
         <v>0</v>
@@ -18305,7 +18314,7 @@
         <v>569</v>
       </c>
       <c r="E566" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F566" t="n">
         <v>0</v>
@@ -18336,7 +18345,7 @@
         <v>570</v>
       </c>
       <c r="E567" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F567" t="n">
         <v>0</v>
@@ -18367,7 +18376,7 @@
         <v>571</v>
       </c>
       <c r="E568" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F568" t="n">
         <v>0</v>
@@ -18429,7 +18438,7 @@
         <v>573</v>
       </c>
       <c r="E570" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F570" t="n">
         <v>0</v>
@@ -18460,7 +18469,7 @@
         <v>574</v>
       </c>
       <c r="E571" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F571" t="n">
         <v>0</v>
@@ -18491,7 +18500,7 @@
         <v>575</v>
       </c>
       <c r="E572" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F572" t="n">
         <v>0</v>
@@ -18553,7 +18562,7 @@
         <v>577</v>
       </c>
       <c r="E574" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F574" t="n">
         <v>0</v>
@@ -18584,7 +18593,7 @@
         <v>578</v>
       </c>
       <c r="E575" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F575" t="n">
         <v>0</v>
@@ -18615,7 +18624,7 @@
         <v>579</v>
       </c>
       <c r="E576" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F576" t="n">
         <v>0</v>
@@ -18708,7 +18717,7 @@
         <v>582</v>
       </c>
       <c r="E579" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F579" t="n">
         <v>0</v>
@@ -18739,7 +18748,7 @@
         <v>583</v>
       </c>
       <c r="E580" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F580" t="n">
         <v>0</v>
@@ -18801,7 +18810,7 @@
         <v>585</v>
       </c>
       <c r="E582" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F582" t="n">
         <v>0</v>
@@ -18925,7 +18934,7 @@
         <v>589</v>
       </c>
       <c r="E586" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F586" t="n">
         <v>0</v>
@@ -18987,7 +18996,7 @@
         <v>591</v>
       </c>
       <c r="E588" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F588" t="n">
         <v>0</v>
@@ -19018,7 +19027,7 @@
         <v>592</v>
       </c>
       <c r="E589" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F589" t="n">
         <v>0</v>
@@ -19080,7 +19089,7 @@
         <v>594</v>
       </c>
       <c r="E591" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F591" t="n">
         <v>0</v>
@@ -19111,7 +19120,7 @@
         <v>595</v>
       </c>
       <c r="E592" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F592" t="n">
         <v>0</v>
@@ -19142,7 +19151,7 @@
         <v>596</v>
       </c>
       <c r="E593" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F593" t="n">
         <v>0</v>
@@ -19173,7 +19182,7 @@
         <v>597</v>
       </c>
       <c r="E594" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F594" t="n">
         <v>0</v>
@@ -19204,7 +19213,7 @@
         <v>598</v>
       </c>
       <c r="E595" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F595" t="n">
         <v>0</v>
@@ -19235,7 +19244,7 @@
         <v>599</v>
       </c>
       <c r="E596" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F596" t="n">
         <v>0</v>
@@ -19266,7 +19275,7 @@
         <v>600</v>
       </c>
       <c r="E597" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F597" t="n">
         <v>0</v>
@@ -19297,7 +19306,7 @@
         <v>601</v>
       </c>
       <c r="E598" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F598" t="n">
         <v>0</v>
@@ -19328,7 +19337,7 @@
         <v>602</v>
       </c>
       <c r="E599" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F599" t="n">
         <v>0</v>
@@ -19390,7 +19399,7 @@
         <v>604</v>
       </c>
       <c r="E601" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F601" t="n">
         <v>0</v>
@@ -19421,7 +19430,7 @@
         <v>605</v>
       </c>
       <c r="E602" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F602" t="n">
         <v>0</v>
@@ -19452,7 +19461,7 @@
         <v>606</v>
       </c>
       <c r="E603" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F603" t="n">
         <v>0</v>
@@ -19514,7 +19523,7 @@
         <v>608</v>
       </c>
       <c r="E605" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F605" t="n">
         <v>0</v>
@@ -19545,7 +19554,7 @@
         <v>609</v>
       </c>
       <c r="E606" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F606" t="n">
         <v>0</v>
@@ -19576,7 +19585,7 @@
         <v>610</v>
       </c>
       <c r="E607" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F607" t="n">
         <v>0</v>
@@ -19607,7 +19616,7 @@
         <v>611</v>
       </c>
       <c r="E608" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F608" t="n">
         <v>0</v>
@@ -19638,7 +19647,7 @@
         <v>612</v>
       </c>
       <c r="E609" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F609" t="n">
         <v>0</v>
@@ -19669,7 +19678,7 @@
         <v>613</v>
       </c>
       <c r="E610" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F610" t="n">
         <v>0</v>
@@ -19762,7 +19771,7 @@
         <v>616</v>
       </c>
       <c r="E613" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F613" t="n">
         <v>0</v>
@@ -19793,7 +19802,7 @@
         <v>617</v>
       </c>
       <c r="E614" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F614" t="n">
         <v>0</v>
@@ -19824,7 +19833,7 @@
         <v>618</v>
       </c>
       <c r="E615" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F615" t="n">
         <v>0</v>
@@ -19855,7 +19864,7 @@
         <v>619</v>
       </c>
       <c r="E616" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F616" t="n">
         <v>0</v>
@@ -19917,7 +19926,7 @@
         <v>621</v>
       </c>
       <c r="E618" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F618" t="n">
         <v>0</v>
@@ -19948,7 +19957,7 @@
         <v>622</v>
       </c>
       <c r="E619" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F619" t="n">
         <v>0</v>
@@ -19979,7 +19988,7 @@
         <v>623</v>
       </c>
       <c r="E620" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F620" t="n">
         <v>0</v>
@@ -20010,7 +20019,7 @@
         <v>624</v>
       </c>
       <c r="E621" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F621" t="n">
         <v>0</v>
@@ -20041,7 +20050,7 @@
         <v>625</v>
       </c>
       <c r="E622" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F622" t="n">
         <v>0</v>
@@ -20072,7 +20081,7 @@
         <v>626</v>
       </c>
       <c r="E623" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F623" t="n">
         <v>0</v>
@@ -20134,7 +20143,7 @@
         <v>628</v>
       </c>
       <c r="E625" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F625" t="n">
         <v>0</v>
@@ -20227,7 +20236,7 @@
         <v>631</v>
       </c>
       <c r="E628" t="n">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F628" t="n">
         <v>0</v>
@@ -20289,7 +20298,7 @@
         <v>633</v>
       </c>
       <c r="E630" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F630" t="n">
         <v>0</v>
@@ -20320,7 +20329,7 @@
         <v>634</v>
       </c>
       <c r="E631" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F631" t="n">
         <v>0</v>
@@ -20351,7 +20360,7 @@
         <v>635</v>
       </c>
       <c r="E632" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F632" t="n">
         <v>0</v>
@@ -20382,7 +20391,7 @@
         <v>636</v>
       </c>
       <c r="E633" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F633" t="n">
         <v>0</v>
@@ -20444,7 +20453,7 @@
         <v>638</v>
       </c>
       <c r="E635" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F635" t="n">
         <v>0</v>
@@ -20475,7 +20484,7 @@
         <v>639</v>
       </c>
       <c r="E636" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F636" t="n">
         <v>0</v>
@@ -20506,7 +20515,7 @@
         <v>640</v>
       </c>
       <c r="E637" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F637" t="n">
         <v>0</v>
@@ -20537,7 +20546,7 @@
         <v>641</v>
       </c>
       <c r="E638" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F638" t="n">
         <v>0</v>
@@ -20599,7 +20608,7 @@
         <v>643</v>
       </c>
       <c r="E640" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F640" t="n">
         <v>0</v>
@@ -20630,7 +20639,7 @@
         <v>644</v>
       </c>
       <c r="E641" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F641" t="n">
         <v>0</v>
@@ -20661,7 +20670,7 @@
         <v>645</v>
       </c>
       <c r="E642" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F642" t="n">
         <v>0</v>
@@ -20692,7 +20701,7 @@
         <v>646</v>
       </c>
       <c r="E643" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F643" t="n">
         <v>0</v>
@@ -20754,7 +20763,7 @@
         <v>648</v>
       </c>
       <c r="E645" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F645" t="n">
         <v>0</v>
@@ -20785,7 +20794,7 @@
         <v>649</v>
       </c>
       <c r="E646" t="n">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F646" t="n">
         <v>0</v>
@@ -20816,7 +20825,7 @@
         <v>650</v>
       </c>
       <c r="E647" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F647" t="n">
         <v>0</v>
@@ -20847,7 +20856,7 @@
         <v>651</v>
       </c>
       <c r="E648" t="n">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F648" t="n">
         <v>0</v>
@@ -20878,7 +20887,7 @@
         <v>652</v>
       </c>
       <c r="E649" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F649" t="n">
         <v>0</v>
@@ -20909,7 +20918,7 @@
         <v>653</v>
       </c>
       <c r="E650" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F650" t="n">
         <v>0</v>
@@ -20940,7 +20949,7 @@
         <v>654</v>
       </c>
       <c r="E651" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F651" t="n">
         <v>0</v>
@@ -21002,7 +21011,7 @@
         <v>656</v>
       </c>
       <c r="E653" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F653" t="n">
         <v>0</v>
@@ -21064,7 +21073,7 @@
         <v>658</v>
       </c>
       <c r="E655" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F655" t="n">
         <v>0</v>
@@ -21095,7 +21104,7 @@
         <v>659</v>
       </c>
       <c r="E656" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F656" t="n">
         <v>0</v>
@@ -21126,7 +21135,7 @@
         <v>660</v>
       </c>
       <c r="E657" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F657" t="n">
         <v>0</v>
@@ -21188,7 +21197,7 @@
         <v>662</v>
       </c>
       <c r="E659" t="n">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F659" t="n">
         <v>0</v>
@@ -21219,7 +21228,7 @@
         <v>663</v>
       </c>
       <c r="E660" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F660" t="n">
         <v>0</v>
@@ -21250,7 +21259,7 @@
         <v>664</v>
       </c>
       <c r="E661" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F661" t="n">
         <v>0</v>
@@ -21281,7 +21290,7 @@
         <v>665</v>
       </c>
       <c r="E662" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F662" t="n">
         <v>0</v>
@@ -21312,7 +21321,7 @@
         <v>666</v>
       </c>
       <c r="E663" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F663" t="n">
         <v>0</v>
@@ -21374,7 +21383,7 @@
         <v>668</v>
       </c>
       <c r="E665" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F665" t="n">
         <v>0</v>
@@ -21405,7 +21414,7 @@
         <v>669</v>
       </c>
       <c r="E666" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F666" t="n">
         <v>0</v>
@@ -21436,7 +21445,7 @@
         <v>670</v>
       </c>
       <c r="E667" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F667" t="n">
         <v>0</v>
@@ -21529,7 +21538,7 @@
         <v>673</v>
       </c>
       <c r="E670" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F670" t="n">
         <v>0</v>
@@ -21591,7 +21600,7 @@
         <v>675</v>
       </c>
       <c r="E672" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F672" t="n">
         <v>0</v>
@@ -21622,7 +21631,7 @@
         <v>676</v>
       </c>
       <c r="E673" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F673" t="n">
         <v>0</v>
@@ -21684,7 +21693,7 @@
         <v>678</v>
       </c>
       <c r="E675" t="n">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F675" t="n">
         <v>0</v>
@@ -21715,7 +21724,7 @@
         <v>679</v>
       </c>
       <c r="E676" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F676" t="n">
         <v>0</v>
@@ -21746,7 +21755,7 @@
         <v>680</v>
       </c>
       <c r="E677" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F677" t="n">
         <v>0</v>
@@ -21777,7 +21786,7 @@
         <v>681</v>
       </c>
       <c r="E678" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F678" t="n">
         <v>0</v>
@@ -21808,7 +21817,7 @@
         <v>682</v>
       </c>
       <c r="E679" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F679" t="n">
         <v>0</v>
@@ -21870,7 +21879,7 @@
         <v>684</v>
       </c>
       <c r="E681" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F681" t="n">
         <v>0</v>
@@ -21901,7 +21910,7 @@
         <v>685</v>
       </c>
       <c r="E682" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F682" t="n">
         <v>0</v>
@@ -21932,7 +21941,7 @@
         <v>686</v>
       </c>
       <c r="E683" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F683" t="n">
         <v>0</v>
@@ -21994,7 +22003,7 @@
         <v>688</v>
       </c>
       <c r="E685" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F685" t="n">
         <v>0</v>
@@ -22087,7 +22096,7 @@
         <v>691</v>
       </c>
       <c r="E688" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F688" t="n">
         <v>0</v>
@@ -22149,7 +22158,7 @@
         <v>693</v>
       </c>
       <c r="E690" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F690" t="n">
         <v>0</v>
@@ -22180,7 +22189,7 @@
         <v>694</v>
       </c>
       <c r="E691" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F691" t="n">
         <v>0</v>
@@ -22211,7 +22220,7 @@
         <v>695</v>
       </c>
       <c r="E692" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F692" t="n">
         <v>0</v>
@@ -22242,7 +22251,7 @@
         <v>696</v>
       </c>
       <c r="E693" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F693" t="n">
         <v>0</v>
@@ -22273,7 +22282,7 @@
         <v>697</v>
       </c>
       <c r="E694" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F694" t="n">
         <v>0</v>
@@ -22335,7 +22344,7 @@
         <v>699</v>
       </c>
       <c r="E696" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F696" t="n">
         <v>0</v>
@@ -22366,7 +22375,7 @@
         <v>700</v>
       </c>
       <c r="E697" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F697" t="n">
         <v>0</v>
@@ -22397,7 +22406,7 @@
         <v>701</v>
       </c>
       <c r="E698" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F698" t="n">
         <v>0</v>
@@ -22428,7 +22437,7 @@
         <v>702</v>
       </c>
       <c r="E699" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F699" t="n">
         <v>0</v>
@@ -22459,7 +22468,7 @@
         <v>703</v>
       </c>
       <c r="E700" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F700" t="n">
         <v>0</v>
@@ -22490,7 +22499,7 @@
         <v>704</v>
       </c>
       <c r="E701" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F701" t="n">
         <v>0</v>
@@ -22521,7 +22530,7 @@
         <v>705</v>
       </c>
       <c r="E702" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F702" t="n">
         <v>0</v>
@@ -22552,7 +22561,7 @@
         <v>706</v>
       </c>
       <c r="E703" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F703" t="n">
         <v>0</v>
@@ -22583,7 +22592,7 @@
         <v>707</v>
       </c>
       <c r="E704" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F704" t="n">
         <v>0</v>
@@ -22614,7 +22623,7 @@
         <v>708</v>
       </c>
       <c r="E705" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F705" t="n">
         <v>0</v>
@@ -22645,7 +22654,7 @@
         <v>709</v>
       </c>
       <c r="E706" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F706" t="n">
         <v>0</v>
@@ -22707,7 +22716,7 @@
         <v>711</v>
       </c>
       <c r="E708" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F708" t="n">
         <v>0</v>
@@ -22738,7 +22747,7 @@
         <v>712</v>
       </c>
       <c r="E709" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F709" t="n">
         <v>0</v>
@@ -22769,7 +22778,7 @@
         <v>713</v>
       </c>
       <c r="E710" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F710" t="n">
         <v>0</v>
@@ -22800,7 +22809,7 @@
         <v>714</v>
       </c>
       <c r="E711" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F711" t="n">
         <v>0</v>
@@ -22831,7 +22840,7 @@
         <v>715</v>
       </c>
       <c r="E712" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F712" t="n">
         <v>0</v>
@@ -22893,7 +22902,7 @@
         <v>717</v>
       </c>
       <c r="E714" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F714" t="n">
         <v>0</v>
@@ -22955,7 +22964,7 @@
         <v>719</v>
       </c>
       <c r="E716" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F716" t="n">
         <v>0</v>
@@ -22986,7 +22995,7 @@
         <v>720</v>
       </c>
       <c r="E717" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F717" t="n">
         <v>0</v>
@@ -23079,7 +23088,7 @@
         <v>723</v>
       </c>
       <c r="E720" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F720" t="n">
         <v>0</v>
@@ -23110,7 +23119,7 @@
         <v>724</v>
       </c>
       <c r="E721" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F721" t="n">
         <v>0</v>
@@ -23141,7 +23150,7 @@
         <v>725</v>
       </c>
       <c r="E722" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F722" t="n">
         <v>0</v>
@@ -23172,7 +23181,7 @@
         <v>726</v>
       </c>
       <c r="E723" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F723" t="n">
         <v>0</v>
@@ -23296,7 +23305,7 @@
         <v>730</v>
       </c>
       <c r="E727" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F727" t="n">
         <v>0</v>
@@ -23327,7 +23336,7 @@
         <v>731</v>
       </c>
       <c r="E728" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F728" t="n">
         <v>0</v>
@@ -23358,7 +23367,7 @@
         <v>732</v>
       </c>
       <c r="E729" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F729" t="n">
         <v>0</v>
@@ -23389,7 +23398,7 @@
         <v>733</v>
       </c>
       <c r="E730" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F730" t="n">
         <v>0</v>
@@ -23420,7 +23429,7 @@
         <v>734</v>
       </c>
       <c r="E731" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F731" t="n">
         <v>0</v>
@@ -23451,7 +23460,7 @@
         <v>735</v>
       </c>
       <c r="E732" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F732" t="n">
         <v>0</v>
@@ -23482,7 +23491,7 @@
         <v>736</v>
       </c>
       <c r="E733" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F733" t="n">
         <v>0</v>
@@ -23513,7 +23522,7 @@
         <v>737</v>
       </c>
       <c r="E734" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F734" t="n">
         <v>0</v>
@@ -23544,7 +23553,7 @@
         <v>738</v>
       </c>
       <c r="E735" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F735" t="n">
         <v>0</v>
@@ -23575,7 +23584,7 @@
         <v>739</v>
       </c>
       <c r="E736" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F736" t="n">
         <v>0</v>
@@ -23606,7 +23615,7 @@
         <v>740</v>
       </c>
       <c r="E737" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F737" t="n">
         <v>0</v>
@@ -23637,7 +23646,7 @@
         <v>741</v>
       </c>
       <c r="E738" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F738" t="n">
         <v>0</v>
@@ -23668,7 +23677,7 @@
         <v>742</v>
       </c>
       <c r="E739" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F739" t="n">
         <v>0</v>
@@ -23730,7 +23739,7 @@
         <v>744</v>
       </c>
       <c r="E741" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F741" t="n">
         <v>0</v>
@@ -23761,7 +23770,7 @@
         <v>745</v>
       </c>
       <c r="E742" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F742" t="n">
         <v>0</v>
@@ -23792,7 +23801,7 @@
         <v>746</v>
       </c>
       <c r="E743" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F743" t="n">
         <v>0</v>
@@ -23854,7 +23863,7 @@
         <v>748</v>
       </c>
       <c r="E745" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F745" t="n">
         <v>0</v>
@@ -23916,7 +23925,7 @@
         <v>750</v>
       </c>
       <c r="E747" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F747" t="n">
         <v>0</v>
@@ -23947,7 +23956,7 @@
         <v>751</v>
       </c>
       <c r="E748" t="n">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F748" t="n">
         <v>0</v>
@@ -23978,7 +23987,7 @@
         <v>752</v>
       </c>
       <c r="E749" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F749" t="n">
         <v>0</v>
@@ -24009,7 +24018,7 @@
         <v>753</v>
       </c>
       <c r="E750" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F750" t="n">
         <v>0</v>
@@ -24040,7 +24049,7 @@
         <v>754</v>
       </c>
       <c r="E751" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F751" t="n">
         <v>0</v>
@@ -24071,7 +24080,7 @@
         <v>755</v>
       </c>
       <c r="E752" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F752" t="n">
         <v>0</v>
@@ -24102,7 +24111,7 @@
         <v>756</v>
       </c>
       <c r="E753" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F753" t="n">
         <v>0</v>
@@ -24133,7 +24142,7 @@
         <v>757</v>
       </c>
       <c r="E754" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F754" t="n">
         <v>0</v>
@@ -24226,7 +24235,7 @@
         <v>760</v>
       </c>
       <c r="E757" t="n">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F757" t="n">
         <v>0</v>
@@ -24257,7 +24266,7 @@
         <v>761</v>
       </c>
       <c r="E758" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F758" t="n">
         <v>0</v>
@@ -24288,7 +24297,7 @@
         <v>762</v>
       </c>
       <c r="E759" t="n">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F759" t="n">
         <v>0</v>
@@ -24350,7 +24359,7 @@
         <v>764</v>
       </c>
       <c r="E761" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F761" t="n">
         <v>0</v>
@@ -24381,7 +24390,7 @@
         <v>765</v>
       </c>
       <c r="E762" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F762" t="n">
         <v>0</v>
@@ -24412,7 +24421,7 @@
         <v>766</v>
       </c>
       <c r="E763" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F763" t="n">
         <v>0</v>
@@ -24443,7 +24452,7 @@
         <v>767</v>
       </c>
       <c r="E764" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F764" t="n">
         <v>0</v>
@@ -24505,7 +24514,7 @@
         <v>769</v>
       </c>
       <c r="E766" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F766" t="n">
         <v>0</v>
@@ -24567,7 +24576,7 @@
         <v>771</v>
       </c>
       <c r="E768" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F768" t="n">
         <v>0</v>
@@ -24598,7 +24607,7 @@
         <v>772</v>
       </c>
       <c r="E769" t="n">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F769" t="n">
         <v>0</v>
@@ -24629,7 +24638,7 @@
         <v>773</v>
       </c>
       <c r="E770" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F770" t="n">
         <v>0</v>
@@ -24660,7 +24669,7 @@
         <v>774</v>
       </c>
       <c r="E771" t="n">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F771" t="n">
         <v>0</v>
@@ -24691,7 +24700,7 @@
         <v>775</v>
       </c>
       <c r="E772" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F772" t="n">
         <v>0</v>
@@ -24753,7 +24762,7 @@
         <v>777</v>
       </c>
       <c r="E774" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F774" t="n">
         <v>0</v>
@@ -24784,7 +24793,7 @@
         <v>778</v>
       </c>
       <c r="E775" t="n">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F775" t="n">
         <v>0</v>
@@ -24815,7 +24824,7 @@
         <v>779</v>
       </c>
       <c r="E776" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F776" t="n">
         <v>0</v>
@@ -24846,7 +24855,7 @@
         <v>780</v>
       </c>
       <c r="E777" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F777" t="n">
         <v>0</v>
@@ -24877,7 +24886,7 @@
         <v>781</v>
       </c>
       <c r="E778" t="n">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F778" t="n">
         <v>0</v>
@@ -24908,7 +24917,7 @@
         <v>782</v>
       </c>
       <c r="E779" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F779" t="n">
         <v>0</v>
@@ -24939,7 +24948,7 @@
         <v>783</v>
       </c>
       <c r="E780" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F780" t="n">
         <v>0</v>
@@ -24970,7 +24979,7 @@
         <v>784</v>
       </c>
       <c r="E781" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F781" t="n">
         <v>0</v>
@@ -25001,7 +25010,7 @@
         <v>785</v>
       </c>
       <c r="E782" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F782" t="n">
         <v>0</v>
@@ -25125,7 +25134,7 @@
         <v>789</v>
       </c>
       <c r="E786" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F786" t="n">
         <v>0</v>
@@ -25218,7 +25227,7 @@
         <v>792</v>
       </c>
       <c r="E789" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F789" t="n">
         <v>0</v>
@@ -25249,7 +25258,7 @@
         <v>793</v>
       </c>
       <c r="E790" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F790" t="n">
         <v>0</v>
@@ -25280,7 +25289,7 @@
         <v>794</v>
       </c>
       <c r="E791" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F791" t="n">
         <v>0</v>
@@ -25311,7 +25320,7 @@
         <v>795</v>
       </c>
       <c r="E792" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F792" t="n">
         <v>0</v>
@@ -25342,7 +25351,7 @@
         <v>796</v>
       </c>
       <c r="E793" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F793" t="n">
         <v>0</v>
@@ -25373,7 +25382,7 @@
         <v>797</v>
       </c>
       <c r="E794" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F794" t="n">
         <v>0</v>
@@ -25404,7 +25413,7 @@
         <v>798</v>
       </c>
       <c r="E795" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F795" t="n">
         <v>0</v>
@@ -25435,7 +25444,7 @@
         <v>799</v>
       </c>
       <c r="E796" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F796" t="n">
         <v>0</v>
@@ -25466,7 +25475,7 @@
         <v>800</v>
       </c>
       <c r="E797" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F797" t="n">
         <v>0</v>
@@ -25497,7 +25506,7 @@
         <v>801</v>
       </c>
       <c r="E798" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F798" t="n">
         <v>0</v>
@@ -25528,7 +25537,7 @@
         <v>802</v>
       </c>
       <c r="E799" t="n">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F799" t="n">
         <v>0</v>
@@ -25559,7 +25568,7 @@
         <v>803</v>
       </c>
       <c r="E800" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F800" t="n">
         <v>0</v>
@@ -25621,7 +25630,7 @@
         <v>805</v>
       </c>
       <c r="E802" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F802" t="n">
         <v>0</v>
@@ -25652,7 +25661,7 @@
         <v>806</v>
       </c>
       <c r="E803" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F803" t="n">
         <v>0</v>
@@ -25683,7 +25692,7 @@
         <v>807</v>
       </c>
       <c r="E804" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F804" t="n">
         <v>0</v>
@@ -25745,7 +25754,7 @@
         <v>809</v>
       </c>
       <c r="E806" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F806" t="n">
         <v>0</v>
@@ -25776,7 +25785,7 @@
         <v>810</v>
       </c>
       <c r="E807" t="n">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F807" t="n">
         <v>0</v>
@@ -25807,7 +25816,7 @@
         <v>811</v>
       </c>
       <c r="E808" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F808" t="n">
         <v>0</v>
@@ -25838,7 +25847,7 @@
         <v>812</v>
       </c>
       <c r="E809" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F809" t="n">
         <v>0</v>
@@ -25869,7 +25878,7 @@
         <v>813</v>
       </c>
       <c r="E810" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F810" t="n">
         <v>0</v>
@@ -25900,7 +25909,7 @@
         <v>814</v>
       </c>
       <c r="E811" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F811" t="n">
         <v>0</v>
@@ -25931,7 +25940,7 @@
         <v>815</v>
       </c>
       <c r="E812" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F812" t="n">
         <v>0</v>
@@ -25962,7 +25971,7 @@
         <v>816</v>
       </c>
       <c r="E813" t="n">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F813" t="n">
         <v>0</v>
@@ -25993,7 +26002,7 @@
         <v>817</v>
       </c>
       <c r="E814" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F814" t="n">
         <v>0</v>
@@ -26024,7 +26033,7 @@
         <v>818</v>
       </c>
       <c r="E815" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F815" t="n">
         <v>0</v>
@@ -26055,7 +26064,7 @@
         <v>819</v>
       </c>
       <c r="E816" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F816" t="n">
         <v>0</v>
@@ -26086,7 +26095,7 @@
         <v>820</v>
       </c>
       <c r="E817" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F817" t="n">
         <v>0</v>
@@ -26117,7 +26126,7 @@
         <v>821</v>
       </c>
       <c r="E818" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F818" t="n">
         <v>0</v>
@@ -26148,7 +26157,7 @@
         <v>822</v>
       </c>
       <c r="E819" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F819" t="n">
         <v>0</v>
@@ -26210,7 +26219,7 @@
         <v>824</v>
       </c>
       <c r="E821" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F821" t="n">
         <v>0</v>
@@ -26241,7 +26250,7 @@
         <v>825</v>
       </c>
       <c r="E822" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F822" t="n">
         <v>0</v>
@@ -26303,7 +26312,7 @@
         <v>827</v>
       </c>
       <c r="E824" t="n">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F824" t="n">
         <v>0</v>
@@ -26365,7 +26374,7 @@
         <v>829</v>
       </c>
       <c r="E826" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F826" t="n">
         <v>0</v>
@@ -26396,7 +26405,7 @@
         <v>830</v>
       </c>
       <c r="E827" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F827" t="n">
         <v>0</v>
@@ -26427,7 +26436,7 @@
         <v>831</v>
       </c>
       <c r="E828" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F828" t="n">
         <v>0</v>
@@ -26489,7 +26498,7 @@
         <v>833</v>
       </c>
       <c r="E830" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F830" t="n">
         <v>0</v>
@@ -26582,7 +26591,7 @@
         <v>836</v>
       </c>
       <c r="E833" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F833" t="n">
         <v>0</v>
@@ -26613,7 +26622,7 @@
         <v>837</v>
       </c>
       <c r="E834" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F834" t="n">
         <v>0</v>
@@ -26644,7 +26653,7 @@
         <v>838</v>
       </c>
       <c r="E835" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F835" t="n">
         <v>0</v>
@@ -26706,7 +26715,7 @@
         <v>840</v>
       </c>
       <c r="E837" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F837" t="n">
         <v>0</v>
@@ -26830,7 +26839,7 @@
         <v>844</v>
       </c>
       <c r="E841" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F841" t="n">
         <v>0</v>
@@ -26892,7 +26901,7 @@
         <v>846</v>
       </c>
       <c r="E843" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F843" t="n">
         <v>0</v>
@@ -26923,7 +26932,7 @@
         <v>847</v>
       </c>
       <c r="E844" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F844" t="n">
         <v>0</v>
@@ -26954,7 +26963,7 @@
         <v>848</v>
       </c>
       <c r="E845" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F845" t="n">
         <v>0</v>
@@ -26985,7 +26994,7 @@
         <v>849</v>
       </c>
       <c r="E846" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F846" t="n">
         <v>0</v>
@@ -27047,7 +27056,7 @@
         <v>851</v>
       </c>
       <c r="E848" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F848" t="n">
         <v>0</v>
@@ -27078,7 +27087,7 @@
         <v>852</v>
       </c>
       <c r="E849" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F849" t="n">
         <v>0</v>
@@ -27109,7 +27118,7 @@
         <v>853</v>
       </c>
       <c r="E850" t="n">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F850" t="n">
         <v>0</v>
@@ -27140,7 +27149,7 @@
         <v>854</v>
       </c>
       <c r="E851" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F851" t="n">
         <v>0</v>
@@ -27171,7 +27180,7 @@
         <v>855</v>
       </c>
       <c r="E852" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F852" t="n">
         <v>0</v>
@@ -27233,7 +27242,7 @@
         <v>857</v>
       </c>
       <c r="E854" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F854" t="n">
         <v>0</v>
@@ -27264,7 +27273,7 @@
         <v>858</v>
       </c>
       <c r="E855" t="n">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F855" t="n">
         <v>0</v>
@@ -27295,7 +27304,7 @@
         <v>859</v>
       </c>
       <c r="E856" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F856" t="n">
         <v>0</v>
@@ -27388,7 +27397,7 @@
         <v>862</v>
       </c>
       <c r="E859" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F859" t="n">
         <v>0</v>
@@ -27450,7 +27459,7 @@
         <v>864</v>
       </c>
       <c r="E861" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F861" t="n">
         <v>0</v>
@@ -27481,7 +27490,7 @@
         <v>865</v>
       </c>
       <c r="E862" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F862" t="n">
         <v>0</v>
@@ -27512,7 +27521,7 @@
         <v>866</v>
       </c>
       <c r="E863" t="n">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F863" t="n">
         <v>0</v>
@@ -27574,7 +27583,7 @@
         <v>868</v>
       </c>
       <c r="E865" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F865" t="n">
         <v>0</v>
@@ -27605,7 +27614,7 @@
         <v>869</v>
       </c>
       <c r="E866" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F866" t="n">
         <v>0</v>
@@ -27636,7 +27645,7 @@
         <v>870</v>
       </c>
       <c r="E867" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F867" t="n">
         <v>0</v>
@@ -27667,7 +27676,7 @@
         <v>871</v>
       </c>
       <c r="E868" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F868" t="n">
         <v>0</v>
@@ -27698,7 +27707,7 @@
         <v>872</v>
       </c>
       <c r="E869" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F869" t="n">
         <v>0</v>
@@ -27729,7 +27738,7 @@
         <v>873</v>
       </c>
       <c r="E870" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F870" t="n">
         <v>0</v>
@@ -27760,7 +27769,7 @@
         <v>874</v>
       </c>
       <c r="E871" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F871" t="n">
         <v>0</v>
@@ -27791,7 +27800,7 @@
         <v>875</v>
       </c>
       <c r="E872" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F872" t="n">
         <v>0</v>
@@ -27822,7 +27831,7 @@
         <v>876</v>
       </c>
       <c r="E873" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F873" t="n">
         <v>0</v>
@@ -27853,7 +27862,7 @@
         <v>877</v>
       </c>
       <c r="E874" t="n">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F874" t="n">
         <v>0</v>
@@ -27915,7 +27924,7 @@
         <v>879</v>
       </c>
       <c r="E876" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F876" t="n">
         <v>0</v>
@@ -27946,7 +27955,7 @@
         <v>880</v>
       </c>
       <c r="E877" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F877" t="n">
         <v>0</v>
@@ -28008,7 +28017,7 @@
         <v>882</v>
       </c>
       <c r="E879" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F879" t="n">
         <v>0</v>
@@ -28039,7 +28048,7 @@
         <v>883</v>
       </c>
       <c r="E880" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F880" t="n">
         <v>0</v>
@@ -28070,7 +28079,7 @@
         <v>884</v>
       </c>
       <c r="E881" t="n">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F881" t="n">
         <v>0</v>
@@ -28101,7 +28110,7 @@
         <v>885</v>
       </c>
       <c r="E882" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F882" t="n">
         <v>0</v>
@@ -28132,7 +28141,7 @@
         <v>886</v>
       </c>
       <c r="E883" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F883" t="n">
         <v>0</v>
@@ -28225,7 +28234,7 @@
         <v>889</v>
       </c>
       <c r="E886" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F886" t="n">
         <v>0</v>
@@ -28287,7 +28296,7 @@
         <v>891</v>
       </c>
       <c r="E888" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F888" t="n">
         <v>0</v>
@@ -28318,7 +28327,7 @@
         <v>892</v>
       </c>
       <c r="E889" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F889" t="n">
         <v>0</v>
@@ -28380,7 +28389,7 @@
         <v>894</v>
       </c>
       <c r="E891" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F891" t="n">
         <v>0</v>
@@ -28442,7 +28451,7 @@
         <v>896</v>
       </c>
       <c r="E893" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F893" t="n">
         <v>0</v>
@@ -28504,7 +28513,7 @@
         <v>898</v>
       </c>
       <c r="E895" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F895" t="n">
         <v>0</v>
@@ -28566,7 +28575,7 @@
         <v>900</v>
       </c>
       <c r="E897" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F897" t="n">
         <v>0</v>
@@ -28597,7 +28606,7 @@
         <v>901</v>
       </c>
       <c r="E898" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F898" t="n">
         <v>0</v>
@@ -28628,7 +28637,7 @@
         <v>902</v>
       </c>
       <c r="E899" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F899" t="n">
         <v>0</v>
@@ -28659,7 +28668,7 @@
         <v>903</v>
       </c>
       <c r="E900" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F900" t="n">
         <v>0</v>
@@ -28690,7 +28699,7 @@
         <v>904</v>
       </c>
       <c r="E901" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F901" t="n">
         <v>0</v>
@@ -28752,7 +28761,7 @@
         <v>906</v>
       </c>
       <c r="E903" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F903" t="n">
         <v>0</v>
@@ -28845,7 +28854,7 @@
         <v>909</v>
       </c>
       <c r="E906" t="n">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F906" t="n">
         <v>0</v>
@@ -28876,7 +28885,7 @@
         <v>910</v>
       </c>
       <c r="E907" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F907" t="n">
         <v>0</v>
@@ -28907,7 +28916,7 @@
         <v>911</v>
       </c>
       <c r="E908" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F908" t="n">
         <v>0</v>
@@ -28938,7 +28947,7 @@
         <v>912</v>
       </c>
       <c r="E909" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F909" t="n">
         <v>0</v>
@@ -28969,7 +28978,7 @@
         <v>913</v>
       </c>
       <c r="E910" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F910" t="n">
         <v>0</v>
@@ -29000,7 +29009,7 @@
         <v>914</v>
       </c>
       <c r="E911" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F911" t="n">
         <v>0</v>
@@ -29031,7 +29040,7 @@
         <v>915</v>
       </c>
       <c r="E912" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F912" t="n">
         <v>0</v>
@@ -29062,7 +29071,7 @@
         <v>916</v>
       </c>
       <c r="E913" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F913" t="n">
         <v>0</v>
@@ -29093,7 +29102,7 @@
         <v>917</v>
       </c>
       <c r="E914" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F914" t="n">
         <v>0</v>
@@ -29124,7 +29133,7 @@
         <v>918</v>
       </c>
       <c r="E915" t="n">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F915" t="n">
         <v>0</v>
@@ -29155,7 +29164,7 @@
         <v>919</v>
       </c>
       <c r="E916" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F916" t="n">
         <v>0</v>
@@ -29186,7 +29195,7 @@
         <v>920</v>
       </c>
       <c r="E917" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F917" t="n">
         <v>0</v>
@@ -29217,7 +29226,7 @@
         <v>921</v>
       </c>
       <c r="E918" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F918" t="n">
         <v>0</v>
@@ -29248,7 +29257,7 @@
         <v>922</v>
       </c>
       <c r="E919" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F919" t="n">
         <v>0</v>
@@ -29279,7 +29288,7 @@
         <v>923</v>
       </c>
       <c r="E920" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F920" t="n">
         <v>0</v>
@@ -29310,7 +29319,7 @@
         <v>924</v>
       </c>
       <c r="E921" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F921" t="n">
         <v>0</v>
@@ -29341,7 +29350,7 @@
         <v>925</v>
       </c>
       <c r="E922" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F922" t="n">
         <v>0</v>
@@ -29403,7 +29412,7 @@
         <v>927</v>
       </c>
       <c r="E924" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F924" t="n">
         <v>0</v>
@@ -29527,7 +29536,7 @@
         <v>931</v>
       </c>
       <c r="E928" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F928" t="n">
         <v>0</v>
@@ -29589,7 +29598,7 @@
         <v>933</v>
       </c>
       <c r="E930" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F930" t="n">
         <v>0</v>
@@ -29620,7 +29629,7 @@
         <v>934</v>
       </c>
       <c r="E931" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F931" t="n">
         <v>0</v>
@@ -29651,7 +29660,7 @@
         <v>935</v>
       </c>
       <c r="E932" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F932" t="n">
         <v>0</v>
@@ -29682,7 +29691,7 @@
         <v>936</v>
       </c>
       <c r="E933" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F933" t="n">
         <v>0</v>
@@ -29713,7 +29722,7 @@
         <v>937</v>
       </c>
       <c r="E934" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F934" t="n">
         <v>0</v>
@@ -29744,7 +29753,7 @@
         <v>938</v>
       </c>
       <c r="E935" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F935" t="n">
         <v>0</v>
@@ -29775,7 +29784,7 @@
         <v>939</v>
       </c>
       <c r="E936" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F936" t="n">
         <v>0</v>
@@ -29806,7 +29815,7 @@
         <v>940</v>
       </c>
       <c r="E937" t="n">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F937" t="n">
         <v>0</v>
@@ -29837,7 +29846,7 @@
         <v>941</v>
       </c>
       <c r="E938" t="n">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F938" t="n">
         <v>0</v>
@@ -29868,7 +29877,7 @@
         <v>942</v>
       </c>
       <c r="E939" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F939" t="n">
         <v>0</v>
@@ -29930,7 +29939,7 @@
         <v>944</v>
       </c>
       <c r="E941" t="n">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F941" t="n">
         <v>0</v>
@@ -29992,7 +30001,7 @@
         <v>946</v>
       </c>
       <c r="E943" t="n">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F943" t="n">
         <v>0</v>
@@ -30023,7 +30032,7 @@
         <v>947</v>
       </c>
       <c r="E944" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F944" t="n">
         <v>0</v>
@@ -30054,7 +30063,7 @@
         <v>948</v>
       </c>
       <c r="E945" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F945" t="n">
         <v>0</v>
@@ -30085,7 +30094,7 @@
         <v>949</v>
       </c>
       <c r="E946" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F946" t="n">
         <v>0</v>
@@ -30147,7 +30156,7 @@
         <v>951</v>
       </c>
       <c r="E948" t="n">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F948" t="n">
         <v>0</v>
@@ -30209,7 +30218,7 @@
         <v>953</v>
       </c>
       <c r="E950" t="n">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F950" t="n">
         <v>0</v>
@@ -30240,7 +30249,7 @@
         <v>954</v>
       </c>
       <c r="E951" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F951" t="n">
         <v>0</v>
@@ -30271,7 +30280,7 @@
         <v>955</v>
       </c>
       <c r="E952" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F952" t="n">
         <v>0</v>
@@ -30302,7 +30311,7 @@
         <v>956</v>
       </c>
       <c r="E953" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F953" t="n">
         <v>0</v>
@@ -30364,7 +30373,7 @@
         <v>958</v>
       </c>
       <c r="E955" t="n">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F955" t="n">
         <v>0</v>
@@ -30395,7 +30404,7 @@
         <v>959</v>
       </c>
       <c r="E956" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F956" t="n">
         <v>0</v>
@@ -30426,7 +30435,7 @@
         <v>960</v>
       </c>
       <c r="E957" t="n">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F957" t="n">
         <v>0</v>
@@ -30488,7 +30497,7 @@
         <v>962</v>
       </c>
       <c r="E959" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F959" t="n">
         <v>0</v>
@@ -30519,7 +30528,7 @@
         <v>963</v>
       </c>
       <c r="E960" t="n">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F960" t="n">
         <v>0</v>
@@ -30550,7 +30559,7 @@
         <v>964</v>
       </c>
       <c r="E961" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F961" t="n">
         <v>0</v>
@@ -30643,7 +30652,7 @@
         <v>967</v>
       </c>
       <c r="E964" t="n">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F964" t="n">
         <v>0</v>
@@ -30674,7 +30683,7 @@
         <v>968</v>
       </c>
       <c r="E965" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F965" t="n">
         <v>0</v>
@@ -30705,7 +30714,7 @@
         <v>969</v>
       </c>
       <c r="E966" t="n">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F966" t="n">
         <v>0</v>
@@ -30736,7 +30745,7 @@
         <v>970</v>
       </c>
       <c r="E967" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F967" t="n">
         <v>0</v>
@@ -30767,7 +30776,7 @@
         <v>971</v>
       </c>
       <c r="E968" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F968" t="n">
         <v>0</v>
@@ -30829,7 +30838,7 @@
         <v>973</v>
       </c>
       <c r="E970" t="n">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F970" t="n">
         <v>0</v>
@@ -30860,7 +30869,7 @@
         <v>974</v>
       </c>
       <c r="E971" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F971" t="n">
         <v>0</v>
@@ -30891,7 +30900,7 @@
         <v>975</v>
       </c>
       <c r="E972" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F972" t="n">
         <v>0</v>
@@ -30922,7 +30931,7 @@
         <v>976</v>
       </c>
       <c r="E973" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F973" t="n">
         <v>0</v>
@@ -30953,7 +30962,7 @@
         <v>977</v>
       </c>
       <c r="E974" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F974" t="n">
         <v>0</v>
@@ -30984,7 +30993,7 @@
         <v>978</v>
       </c>
       <c r="E975" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F975" t="n">
         <v>0</v>
@@ -31015,7 +31024,7 @@
         <v>979</v>
       </c>
       <c r="E976" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F976" t="n">
         <v>0</v>
@@ -31046,7 +31055,7 @@
         <v>980</v>
       </c>
       <c r="E977" t="n">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F977" t="n">
         <v>0</v>
@@ -31077,7 +31086,7 @@
         <v>981</v>
       </c>
       <c r="E978" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F978" t="n">
         <v>0</v>
@@ -31108,7 +31117,7 @@
         <v>982</v>
       </c>
       <c r="E979" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F979" t="n">
         <v>0</v>
@@ -31139,7 +31148,7 @@
         <v>983</v>
       </c>
       <c r="E980" t="n">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F980" t="n">
         <v>0</v>
@@ -31170,7 +31179,7 @@
         <v>984</v>
       </c>
       <c r="E981" t="n">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F981" t="n">
         <v>0</v>
@@ -31201,7 +31210,7 @@
         <v>985</v>
       </c>
       <c r="E982" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F982" t="n">
         <v>0</v>
@@ -31232,7 +31241,7 @@
         <v>986</v>
       </c>
       <c r="E983" t="n">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F983" t="n">
         <v>0</v>
@@ -31263,7 +31272,7 @@
         <v>987</v>
       </c>
       <c r="E984" t="n">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F984" t="n">
         <v>0</v>
@@ -31294,7 +31303,7 @@
         <v>988</v>
       </c>
       <c r="E985" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F985" t="n">
         <v>0</v>
@@ -31356,7 +31365,7 @@
         <v>990</v>
       </c>
       <c r="E987" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F987" t="n">
         <v>0</v>
@@ -31387,7 +31396,7 @@
         <v>991</v>
       </c>
       <c r="E988" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F988" t="n">
         <v>0</v>
@@ -31449,7 +31458,7 @@
         <v>993</v>
       </c>
       <c r="E990" t="n">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F990" t="n">
         <v>0</v>
@@ -31542,7 +31551,7 @@
         <v>996</v>
       </c>
       <c r="E993" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F993" t="n">
         <v>0</v>
@@ -31573,7 +31582,7 @@
         <v>997</v>
       </c>
       <c r="E994" t="n">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F994" t="n">
         <v>0</v>
@@ -31604,7 +31613,7 @@
         <v>998</v>
       </c>
       <c r="E995" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F995" t="n">
         <v>0</v>
@@ -31635,7 +31644,7 @@
         <v>999</v>
       </c>
       <c r="E996" t="n">
-        <v>999</v>
+        <v>241</v>
       </c>
       <c r="F996" t="n">
         <v>0</v>
@@ -31666,7 +31675,7 @@
         <v>999</v>
       </c>
       <c r="E997" t="n">
-        <v>999</v>
+        <v>137</v>
       </c>
       <c r="F997" t="n">
         <v>0</v>
@@ -31697,7 +31706,7 @@
         <v>999</v>
       </c>
       <c r="E998" t="n">
-        <v>999</v>
+        <v>138</v>
       </c>
       <c r="F998" t="n">
         <v>0</v>
@@ -31728,7 +31737,7 @@
         <v>999</v>
       </c>
       <c r="E999" t="n">
-        <v>999</v>
+        <v>418</v>
       </c>
       <c r="F999" t="n">
         <v>0</v>

--- a/players.xlsx
+++ b/players.xlsx
@@ -617,7 +617,7 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -750,10 +750,10 @@
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -886,10 +886,10 @@
         <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
         <v>90</v>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18">
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E22" t="n">
         <v>20</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E25" t="n">
         <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27" t="n">
         <v>9</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30">
@@ -1467,7 +1467,7 @@
         <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31" t="n">
         <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E32" t="n">
         <v>14</v>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>92</v>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E34" t="n">
         <v>17</v>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E35" t="n">
         <v>18</v>
       </c>
       <c r="F35" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
@@ -1671,7 +1671,7 @@
         <v>12</v>
       </c>
       <c r="F36" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" t="n">
         <v>17</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E38" t="n">
         <v>18</v>
       </c>
       <c r="F38" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39">
@@ -1764,13 +1764,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39" t="n">
         <v>19</v>
       </c>
       <c r="F39" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40">
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E40" t="n">
         <v>26</v>
       </c>
       <c r="F40" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E41" t="n">
         <v>20</v>
@@ -1906,7 +1906,7 @@
         <v>25</v>
       </c>
       <c r="F43" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44">
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E44" t="n">
         <v>21</v>
       </c>
       <c r="F44" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E45" t="n">
         <v>21</v>
       </c>
       <c r="F45" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F46" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47">
@@ -2076,7 +2076,7 @@
         <v>23</v>
       </c>
       <c r="F48" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E50" t="n">
         <v>19</v>
@@ -2178,7 +2178,7 @@
         <v>26</v>
       </c>
       <c r="F51" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52">
@@ -2212,7 +2212,7 @@
         <v>27</v>
       </c>
       <c r="F52" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -2274,13 +2274,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55">
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E55" t="n">
         <v>28</v>
       </c>
       <c r="F55" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E56" t="n">
         <v>29</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E57" t="n">
         <v>27</v>
@@ -2410,13 +2410,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E58" t="n">
         <v>13</v>
       </c>
       <c r="F58" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59">
@@ -2484,7 +2484,7 @@
         <v>22</v>
       </c>
       <c r="F60" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E62" t="n">
         <v>29</v>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64">
@@ -2620,7 +2620,7 @@
         <v>25</v>
       </c>
       <c r="F64" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65">
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E68" t="n">
         <v>24</v>
       </c>
       <c r="F68" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E69" t="n">
         <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70">
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F70" t="n">
         <v>84</v>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E71" t="n">
         <v>6</v>
@@ -2883,13 +2883,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E72" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F73" t="n">
         <v>82</v>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E74" t="n">
         <v>33</v>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E75" t="n">
         <v>5</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E76" t="n">
         <v>34</v>
       </c>
       <c r="F76" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77">
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E77" t="n">
         <v>35</v>
       </c>
       <c r="F77" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78">
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F78" t="n">
         <v>85</v>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E79" t="n">
         <v>33</v>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E80" t="n">
         <v>8</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E81" t="n">
         <v>37</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E82" t="n">
         <v>38</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E83" t="n">
         <v>30</v>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E84" t="n">
         <v>7</v>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F85" t="n">
         <v>85</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E86" t="n">
         <v>32</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E87" t="n">
         <v>31</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E88" t="n">
         <v>39</v>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E89" t="n">
         <v>9</v>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E90" t="n">
         <v>10</v>
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="93">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E93" t="n">
         <v>40</v>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E94" t="n">
         <v>11</v>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
         <v>74</v>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E96" t="n">
         <v>12</v>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E97" t="n">
         <v>35</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E98" t="n">
         <v>41</v>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E99" t="n">
         <v>42</v>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E100" t="n">
         <v>13</v>
       </c>
       <c r="F100" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101">
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E101" t="n">
         <v>43</v>
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E102" t="n">
         <v>37</v>
       </c>
       <c r="F102" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E104" t="n">
         <v>39</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E105" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E106" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E107" t="n">
         <v>46</v>
@@ -4089,10 +4089,10 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F108" t="n">
         <v>87</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E109" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E110" t="n">
         <v>36</v>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E111" t="n">
         <v>63</v>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E112" t="n">
         <v>50</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E113" t="n">
         <v>40</v>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E114" t="n">
         <v>14</v>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E115" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E116" t="n">
         <v>41</v>
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E117" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E118" t="n">
         <v>42</v>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E119" t="n">
         <v>51</v>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E120" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E121" t="n">
         <v>43</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E122" t="n">
         <v>52</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E123" t="n">
         <v>53</v>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E124" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E125" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E126" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E127" t="n">
         <v>15</v>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E128" t="n">
         <v>54</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E129" t="n">
         <v>55</v>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E130" t="n">
         <v>16</v>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E131" t="n">
         <v>36</v>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E132" t="n">
         <v>17</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E133" t="n">
         <v>18</v>
@@ -4904,18 +4904,21 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E134" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>11581</t>
         </is>
+      </c>
+      <c r="H134" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="135">
@@ -4935,7 +4938,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E135" t="n">
         <v>19</v>
@@ -4966,7 +4969,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E136" t="n">
         <v>56</v>
@@ -5031,10 +5034,10 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E138" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -5062,10 +5065,10 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E139" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -5093,7 +5096,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E140" t="n">
         <v>57</v>
@@ -5124,7 +5127,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E141" t="n">
         <v>13</v>
@@ -5155,7 +5158,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E142" t="n">
         <v>20</v>
@@ -5186,10 +5189,10 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E143" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -5217,10 +5220,10 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E144" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -5248,7 +5251,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E145" t="n">
         <v>58</v>
@@ -5279,18 +5282,21 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E146" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
           <t>12474</t>
         </is>
+      </c>
+      <c r="H146" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="147">
@@ -5310,7 +5316,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E147" t="n">
         <v>21</v>
@@ -5341,10 +5347,10 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E148" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -5372,10 +5378,10 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E149" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -5403,7 +5409,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E150" t="n">
         <v>59</v>
@@ -5434,10 +5440,10 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E151" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -5465,10 +5471,10 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E152" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -5496,10 +5502,10 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E153" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -5527,7 +5533,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E154" t="n">
         <v>60</v>
@@ -5558,7 +5564,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E155" t="n">
         <v>22</v>
@@ -5589,10 +5595,10 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E156" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -5620,10 +5626,10 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E157" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -5651,7 +5657,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E158" t="n">
         <v>61</v>
@@ -5682,7 +5688,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E159" t="n">
         <v>28</v>
@@ -5716,10 +5722,10 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E160" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -5747,7 +5753,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E161" t="n">
         <v>62</v>
@@ -5778,10 +5784,10 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E162" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -5809,7 +5815,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E163" t="n">
         <v>64</v>
@@ -5840,7 +5846,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E164" t="n">
         <v>65</v>
@@ -5871,10 +5877,10 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E165" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -5902,10 +5908,10 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E166" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -5933,7 +5939,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E167" t="n">
         <v>23</v>
@@ -5964,10 +5970,10 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E168" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -6026,10 +6032,10 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E170" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -6057,7 +6063,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E171" t="n">
         <v>24</v>
@@ -6088,10 +6094,10 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E172" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -6119,10 +6125,10 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E173" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -6150,7 +6156,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E174" t="n">
         <v>66</v>
@@ -6181,7 +6187,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E175" t="n">
         <v>25</v>
@@ -6212,18 +6218,21 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="E176" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
           <t>9228</t>
         </is>
+      </c>
+      <c r="H176" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="177">
@@ -6243,10 +6252,10 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E177" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -6274,7 +6283,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E178" t="n">
         <v>26</v>
@@ -6305,7 +6314,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E179" t="n">
         <v>27</v>
@@ -6336,7 +6345,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E180" t="n">
         <v>28</v>
@@ -6367,7 +6376,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E181" t="n">
         <v>29</v>
@@ -6398,10 +6407,10 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E182" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -6429,7 +6438,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E183" t="n">
         <v>30</v>
@@ -6460,7 +6469,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E184" t="n">
         <v>31</v>
@@ -6491,7 +6500,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E185" t="n">
         <v>67</v>
@@ -6522,7 +6531,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E186" t="n">
         <v>68</v>
@@ -6553,10 +6562,10 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E187" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -6584,7 +6593,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E188" t="n">
         <v>32</v>
@@ -6615,10 +6624,10 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E189" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -6646,7 +6655,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E190" t="n">
         <v>69</v>
@@ -6677,7 +6686,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E191" t="n">
         <v>70</v>
@@ -6708,10 +6717,10 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E192" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -6739,7 +6748,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E193" t="n">
         <v>71</v>
@@ -6770,7 +6779,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E194" t="n">
         <v>33</v>
@@ -6801,18 +6810,21 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E195" t="n">
         <v>49</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
           <t>13346</t>
         </is>
+      </c>
+      <c r="H195" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="196">
@@ -6832,10 +6844,10 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E196" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
@@ -6863,7 +6875,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E197" t="n">
         <v>72</v>
@@ -6894,10 +6906,10 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E198" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -6925,7 +6937,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E199" t="n">
         <v>73</v>
@@ -6956,7 +6968,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E200" t="n">
         <v>74</v>
@@ -6987,10 +6999,10 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E201" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F201" t="n">
         <v>0</v>
@@ -7024,7 +7036,7 @@
         <v>23</v>
       </c>
       <c r="F202" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -7032,7 +7044,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="203">
@@ -7052,7 +7064,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E203" t="n">
         <v>44</v>
@@ -7083,7 +7095,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E204" t="n">
         <v>75</v>
@@ -7114,7 +7126,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E205" t="n">
         <v>76</v>
@@ -7145,7 +7157,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E206" t="n">
         <v>77</v>
@@ -7176,7 +7188,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E207" t="n">
         <v>78</v>
@@ -7207,10 +7219,10 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E208" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
@@ -7238,10 +7250,10 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E209" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
@@ -7269,10 +7281,10 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E210" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -7300,7 +7312,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E211" t="n">
         <v>79</v>
@@ -7331,10 +7343,10 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E212" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
@@ -7362,7 +7374,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E213" t="n">
         <v>80</v>
@@ -7393,7 +7405,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E214" t="n">
         <v>81</v>
@@ -7424,10 +7436,10 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E215" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
@@ -7455,7 +7467,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E216" t="n">
         <v>38</v>
@@ -7486,7 +7498,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E217" t="n">
         <v>82</v>
@@ -7517,10 +7529,10 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E218" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -7548,7 +7560,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E219" t="n">
         <v>29</v>
@@ -7579,7 +7591,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E220" t="n">
         <v>83</v>
@@ -7610,7 +7622,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E221" t="n">
         <v>48</v>
@@ -7641,7 +7653,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E222" t="n">
         <v>84</v>
@@ -7672,7 +7684,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E223" t="n">
         <v>34</v>
@@ -7703,7 +7715,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E224" t="n">
         <v>85</v>
@@ -7734,7 +7746,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E225" t="n">
         <v>86</v>
@@ -7765,7 +7777,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E226" t="n">
         <v>45</v>
@@ -7799,10 +7811,10 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E227" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -7830,10 +7842,10 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E228" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
@@ -7861,7 +7873,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E229" t="n">
         <v>87</v>
@@ -7892,7 +7904,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E230" t="n">
         <v>88</v>
@@ -7923,7 +7935,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E231" t="n">
         <v>89</v>
@@ -7954,7 +7966,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E232" t="n">
         <v>90</v>
@@ -7985,7 +7997,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E233" t="n">
         <v>91</v>
@@ -8016,10 +8028,10 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E234" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
@@ -8047,7 +8059,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E235" t="n">
         <v>92</v>
@@ -8078,10 +8090,10 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E236" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -8109,10 +8121,10 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E237" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
@@ -8140,10 +8152,10 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E238" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -8171,7 +8183,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E239" t="n">
         <v>93</v>
@@ -8202,10 +8214,10 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E240" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -8233,7 +8245,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E241" t="n">
         <v>94</v>
@@ -8264,7 +8276,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E242" t="n">
         <v>95</v>
@@ -8295,7 +8307,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E243" t="n">
         <v>96</v>
@@ -8326,7 +8338,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E244" t="n">
         <v>97</v>
@@ -8357,7 +8369,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E245" t="n">
         <v>98</v>
@@ -8388,7 +8400,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E246" t="n">
         <v>99</v>
@@ -8419,7 +8431,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E247" t="n">
         <v>100</v>
@@ -8450,7 +8462,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E248" t="n">
         <v>101</v>
@@ -8481,7 +8493,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E249" t="n">
         <v>102</v>
@@ -8512,7 +8524,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E250" t="n">
         <v>103</v>
@@ -8543,7 +8555,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E251" t="n">
         <v>104</v>
@@ -8574,7 +8586,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E252" t="n">
         <v>105</v>
@@ -8605,10 +8617,10 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E253" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F253" t="n">
         <v>0</v>
@@ -8636,7 +8648,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E254" t="n">
         <v>106</v>
@@ -8667,7 +8679,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E255" t="n">
         <v>30</v>
@@ -8698,10 +8710,10 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E256" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F256" t="n">
         <v>0</v>
@@ -8729,7 +8741,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E257" t="n">
         <v>107</v>
@@ -8760,7 +8772,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E258" t="n">
         <v>108</v>
@@ -8791,7 +8803,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E259" t="n">
         <v>31</v>
@@ -8822,7 +8834,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E260" t="n">
         <v>109</v>
@@ -8853,7 +8865,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E261" t="n">
         <v>110</v>
@@ -8884,7 +8896,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E262" t="n">
         <v>47</v>
@@ -8918,7 +8930,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E263" t="n">
         <v>111</v>
@@ -8949,7 +8961,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E264" t="n">
         <v>112</v>
@@ -8980,7 +8992,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E265" t="n">
         <v>35</v>
@@ -9011,7 +9023,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E266" t="n">
         <v>113</v>
@@ -9042,7 +9054,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E267" t="n">
         <v>114</v>
@@ -9073,10 +9085,10 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E268" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F268" t="n">
         <v>0</v>
@@ -9104,7 +9116,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E269" t="n">
         <v>36</v>
@@ -9135,7 +9147,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E270" t="n">
         <v>37</v>
@@ -9166,7 +9178,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E271" t="n">
         <v>32</v>
@@ -9197,7 +9209,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E272" t="n">
         <v>115</v>
@@ -9228,7 +9240,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E273" t="n">
         <v>38</v>
@@ -9259,10 +9271,10 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E274" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F274" t="n">
         <v>0</v>
@@ -9290,7 +9302,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E275" t="n">
         <v>33</v>
@@ -9321,10 +9333,10 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E276" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F276" t="n">
         <v>0</v>
@@ -9352,7 +9364,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E277" t="n">
         <v>34</v>
@@ -9383,10 +9395,10 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E278" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F278" t="n">
         <v>0</v>
@@ -9414,7 +9426,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E279" t="n">
         <v>116</v>
@@ -9445,7 +9457,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E280" t="n">
         <v>35</v>
@@ -9476,7 +9488,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E281" t="n">
         <v>36</v>
@@ -9507,7 +9519,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E282" t="n">
         <v>37</v>
@@ -9538,7 +9550,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E283" t="n">
         <v>39</v>
@@ -9569,7 +9581,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E284" t="n">
         <v>40</v>
@@ -9600,7 +9612,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E285" t="n">
         <v>117</v>
@@ -9631,10 +9643,10 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E286" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
@@ -9662,10 +9674,10 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E287" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F287" t="n">
         <v>0</v>
@@ -9693,10 +9705,10 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E288" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
@@ -9724,10 +9736,10 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E289" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
@@ -9755,10 +9767,10 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E290" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F290" t="n">
         <v>0</v>
@@ -9786,10 +9798,10 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E291" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F291" t="n">
         <v>0</v>
@@ -9817,7 +9829,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E292" t="n">
         <v>38</v>
@@ -9848,10 +9860,10 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E293" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F293" t="n">
         <v>0</v>
@@ -9879,7 +9891,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E294" t="n">
         <v>118</v>
@@ -9910,7 +9922,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E295" t="n">
         <v>39</v>
@@ -9941,10 +9953,10 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E296" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F296" t="n">
         <v>0</v>
@@ -9972,7 +9984,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E297" t="n">
         <v>119</v>
@@ -10003,7 +10015,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E298" t="n">
         <v>120</v>
@@ -10034,7 +10046,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E299" t="n">
         <v>41</v>
@@ -10065,10 +10077,10 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E300" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F300" t="n">
         <v>0</v>
@@ -10096,7 +10108,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E301" t="n">
         <v>121</v>
@@ -10127,7 +10139,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E302" t="n">
         <v>122</v>
@@ -10158,10 +10170,10 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E303" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F303" t="n">
         <v>0</v>
@@ -10189,7 +10201,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E304" t="n">
         <v>42</v>
@@ -10220,7 +10232,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E305" t="n">
         <v>123</v>
@@ -10251,7 +10263,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E306" t="n">
         <v>40</v>
@@ -10282,7 +10294,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E307" t="n">
         <v>124</v>
@@ -10313,7 +10325,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E308" t="n">
         <v>43</v>
@@ -10344,7 +10356,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E309" t="n">
         <v>125</v>
@@ -10375,7 +10387,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E310" t="n">
         <v>126</v>
@@ -10406,10 +10418,10 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E311" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F311" t="n">
         <v>0</v>
@@ -10437,7 +10449,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E312" t="n">
         <v>41</v>
@@ -10468,7 +10480,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E313" t="n">
         <v>127</v>
@@ -10499,7 +10511,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E314" t="n">
         <v>128</v>
@@ -10530,7 +10542,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E315" t="n">
         <v>44</v>
@@ -10561,7 +10573,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E316" t="n">
         <v>42</v>
@@ -10592,7 +10604,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E317" t="n">
         <v>45</v>
@@ -10623,10 +10635,10 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E318" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F318" t="n">
         <v>0</v>
@@ -10654,7 +10666,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E319" t="n">
         <v>129</v>
@@ -10685,10 +10697,10 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E320" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F320" t="n">
         <v>0</v>
@@ -10716,7 +10728,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E321" t="n">
         <v>46</v>
@@ -10747,10 +10759,10 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E322" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F322" t="n">
         <v>0</v>
@@ -10778,7 +10790,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E323" t="n">
         <v>130</v>
@@ -10809,10 +10821,10 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E324" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F324" t="n">
         <v>0</v>
@@ -10840,7 +10852,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E325" t="n">
         <v>43</v>
@@ -10871,7 +10883,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E326" t="n">
         <v>47</v>
@@ -10902,7 +10914,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E327" t="n">
         <v>44</v>
@@ -10933,7 +10945,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E328" t="n">
         <v>131</v>
@@ -10964,7 +10976,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E329" t="n">
         <v>45</v>
@@ -10995,7 +11007,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E330" t="n">
         <v>48</v>
@@ -11026,7 +11038,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E331" t="n">
         <v>49</v>
@@ -11057,7 +11069,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E332" t="n">
         <v>132</v>
@@ -11088,7 +11100,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E333" t="n">
         <v>133</v>
@@ -11119,7 +11131,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E334" t="n">
         <v>134</v>
@@ -11150,10 +11162,10 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E335" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
@@ -11181,7 +11193,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E336" t="n">
         <v>46</v>
@@ -11212,7 +11224,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E337" t="n">
         <v>47</v>
@@ -11243,7 +11255,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E338" t="n">
         <v>135</v>
@@ -11274,7 +11286,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E339" t="n">
         <v>136</v>
@@ -11305,10 +11317,10 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E340" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F340" t="n">
         <v>0</v>
@@ -11336,7 +11348,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E341" t="n">
         <v>137</v>
@@ -11367,10 +11379,10 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E342" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
@@ -11398,7 +11410,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E343" t="n">
         <v>50</v>
@@ -11429,7 +11441,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E344" t="n">
         <v>138</v>
@@ -11460,7 +11472,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E345" t="n">
         <v>51</v>
@@ -11491,7 +11503,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E346" t="n">
         <v>139</v>
@@ -11522,7 +11534,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E347" t="n">
         <v>140</v>
@@ -11553,10 +11565,10 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E348" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F348" t="n">
         <v>0</v>
@@ -11584,10 +11596,10 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E349" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F349" t="n">
         <v>0</v>
@@ -11615,7 +11627,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E350" t="n">
         <v>141</v>
@@ -11646,7 +11658,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E351" t="n">
         <v>142</v>
@@ -11677,7 +11689,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E352" t="n">
         <v>52</v>
@@ -11708,7 +11720,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E353" t="n">
         <v>48</v>
@@ -11739,10 +11751,10 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E354" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F354" t="n">
         <v>0</v>
@@ -11770,7 +11782,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E355" t="n">
         <v>143</v>
@@ -11801,7 +11813,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E356" t="n">
         <v>49</v>
@@ -11832,7 +11844,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E357" t="n">
         <v>53</v>
@@ -11863,7 +11875,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E358" t="n">
         <v>144</v>
@@ -11894,10 +11906,10 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E359" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F359" t="n">
         <v>0</v>
@@ -11925,7 +11937,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E360" t="n">
         <v>50</v>
@@ -11956,10 +11968,10 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E361" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F361" t="n">
         <v>0</v>
@@ -11987,10 +11999,10 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E362" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F362" t="n">
         <v>0</v>
@@ -12018,7 +12030,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E363" t="n">
         <v>51</v>
@@ -12049,7 +12061,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E364" t="n">
         <v>145</v>
@@ -12080,7 +12092,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E365" t="n">
         <v>146</v>
@@ -12111,7 +12123,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E366" t="n">
         <v>54</v>
@@ -12142,7 +12154,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E367" t="n">
         <v>147</v>
@@ -12173,7 +12185,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E368" t="n">
         <v>148</v>
@@ -12204,10 +12216,10 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E369" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F369" t="n">
         <v>0</v>
@@ -12235,7 +12247,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E370" t="n">
         <v>149</v>
@@ -12266,7 +12278,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E371" t="n">
         <v>150</v>
@@ -12297,7 +12309,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E372" t="n">
         <v>151</v>
@@ -12328,7 +12340,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E373" t="n">
         <v>52</v>
@@ -12359,7 +12371,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E374" t="n">
         <v>152</v>
@@ -12390,10 +12402,10 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E375" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F375" t="n">
         <v>0</v>
@@ -12421,7 +12433,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E376" t="n">
         <v>153</v>
@@ -12452,7 +12464,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E377" t="n">
         <v>55</v>
@@ -12483,7 +12495,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E378" t="n">
         <v>154</v>
@@ -12514,10 +12526,10 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E379" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F379" t="n">
         <v>0</v>
@@ -12545,7 +12557,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E380" t="n">
         <v>155</v>
@@ -12576,7 +12588,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E381" t="n">
         <v>56</v>
@@ -12607,7 +12619,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E382" t="n">
         <v>156</v>
@@ -12638,7 +12650,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E383" t="n">
         <v>157</v>
@@ -12669,7 +12681,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E384" t="n">
         <v>53</v>
@@ -12700,7 +12712,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E385" t="n">
         <v>57</v>
@@ -12731,10 +12743,10 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E386" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F386" t="n">
         <v>0</v>
@@ -12762,7 +12774,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E387" t="n">
         <v>158</v>
@@ -12793,10 +12805,10 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E388" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F388" t="n">
         <v>0</v>
@@ -12824,7 +12836,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E389" t="n">
         <v>54</v>
@@ -12855,7 +12867,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E390" t="n">
         <v>58</v>
@@ -12886,7 +12898,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E391" t="n">
         <v>55</v>
@@ -12917,7 +12929,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E392" t="n">
         <v>159</v>
@@ -12948,7 +12960,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E393" t="n">
         <v>56</v>
@@ -12979,7 +12991,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E394" t="n">
         <v>160</v>
@@ -13010,7 +13022,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E395" t="n">
         <v>161</v>
@@ -13041,7 +13053,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E396" t="n">
         <v>162</v>
@@ -13072,10 +13084,10 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E397" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F397" t="n">
         <v>0</v>
@@ -13103,7 +13115,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E398" t="n">
         <v>163</v>
@@ -13134,7 +13146,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E399" t="n">
         <v>164</v>
@@ -13165,7 +13177,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E400" t="n">
         <v>165</v>
@@ -13196,7 +13208,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E401" t="n">
         <v>166</v>
@@ -13227,7 +13239,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E402" t="n">
         <v>167</v>
@@ -13258,10 +13270,10 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E403" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F403" t="n">
         <v>0</v>
@@ -13289,7 +13301,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E404" t="n">
         <v>168</v>
@@ -13320,7 +13332,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E405" t="n">
         <v>59</v>
@@ -13351,7 +13363,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E406" t="n">
         <v>60</v>
@@ -13382,7 +13394,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E407" t="n">
         <v>169</v>
@@ -13413,7 +13425,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E408" t="n">
         <v>57</v>
@@ -13444,7 +13456,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E409" t="n">
         <v>170</v>
@@ -13475,10 +13487,10 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E410" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F410" t="n">
         <v>0</v>
@@ -13506,7 +13518,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E411" t="n">
         <v>171</v>
@@ -13537,7 +13549,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E412" t="n">
         <v>58</v>
@@ -13568,7 +13580,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E413" t="n">
         <v>172</v>
@@ -13599,7 +13611,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E414" t="n">
         <v>59</v>
@@ -13630,7 +13642,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E415" t="n">
         <v>60</v>
@@ -13661,7 +13673,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E416" t="n">
         <v>173</v>
@@ -13692,7 +13704,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E417" t="n">
         <v>61</v>
@@ -13723,7 +13735,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E418" t="n">
         <v>174</v>
@@ -13754,7 +13766,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E419" t="n">
         <v>62</v>
@@ -13785,7 +13797,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E420" t="n">
         <v>175</v>
@@ -13816,7 +13828,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E421" t="n">
         <v>176</v>
@@ -13847,7 +13859,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E422" t="n">
         <v>61</v>
@@ -13878,10 +13890,10 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E423" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F423" t="n">
         <v>0</v>
@@ -13909,7 +13921,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E424" t="n">
         <v>177</v>
@@ -13940,7 +13952,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E425" t="n">
         <v>63</v>
@@ -13971,7 +13983,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E426" t="n">
         <v>178</v>
@@ -14002,7 +14014,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E427" t="n">
         <v>62</v>
@@ -14033,10 +14045,10 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E428" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F428" t="n">
         <v>0</v>
@@ -14064,10 +14076,10 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E429" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F429" t="n">
         <v>0</v>
@@ -14095,7 +14107,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E430" t="n">
         <v>179</v>
@@ -14126,7 +14138,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E431" t="n">
         <v>63</v>
@@ -14157,7 +14169,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E432" t="n">
         <v>64</v>
@@ -14188,7 +14200,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E433" t="n">
         <v>180</v>
@@ -14219,7 +14231,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E434" t="n">
         <v>65</v>
@@ -14250,10 +14262,10 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E435" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F435" t="n">
         <v>0</v>
@@ -14281,10 +14293,10 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E436" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F436" t="n">
         <v>0</v>
@@ -14312,10 +14324,10 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E437" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F437" t="n">
         <v>0</v>
@@ -14343,7 +14355,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E438" t="n">
         <v>66</v>
@@ -14374,10 +14386,10 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E439" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F439" t="n">
         <v>0</v>
@@ -14405,7 +14417,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E440" t="n">
         <v>67</v>
@@ -14436,7 +14448,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E441" t="n">
         <v>181</v>
@@ -14467,7 +14479,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E442" t="n">
         <v>64</v>
@@ -14498,7 +14510,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E443" t="n">
         <v>65</v>
@@ -14529,7 +14541,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E444" t="n">
         <v>66</v>
@@ -14560,7 +14572,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E445" t="n">
         <v>182</v>
@@ -14591,7 +14603,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E446" t="n">
         <v>183</v>
@@ -14622,7 +14634,7 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E447" t="n">
         <v>68</v>
@@ -14653,7 +14665,7 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E448" t="n">
         <v>184</v>
@@ -14684,7 +14696,7 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E449" t="n">
         <v>185</v>
@@ -14715,7 +14727,7 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E450" t="n">
         <v>186</v>
@@ -14746,10 +14758,10 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E451" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F451" t="n">
         <v>0</v>
@@ -14777,7 +14789,7 @@
         </is>
       </c>
       <c r="D452" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E452" t="n">
         <v>67</v>
@@ -14808,7 +14820,7 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E453" t="n">
         <v>187</v>
@@ -14839,7 +14851,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E454" t="n">
         <v>188</v>
@@ -14870,7 +14882,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E455" t="n">
         <v>189</v>
@@ -14901,7 +14913,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E456" t="n">
         <v>190</v>
@@ -14932,7 +14944,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E457" t="n">
         <v>69</v>
@@ -14963,7 +14975,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E458" t="n">
         <v>70</v>
@@ -14994,10 +15006,10 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E459" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F459" t="n">
         <v>0</v>
@@ -15025,7 +15037,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E460" t="n">
         <v>71</v>
@@ -15056,7 +15068,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E461" t="n">
         <v>72</v>
@@ -15087,10 +15099,10 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E462" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F462" t="n">
         <v>0</v>
@@ -15118,7 +15130,7 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E463" t="n">
         <v>191</v>
@@ -15149,7 +15161,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E464" t="n">
         <v>73</v>
@@ -15180,7 +15192,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E465" t="n">
         <v>74</v>
@@ -15211,7 +15223,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E466" t="n">
         <v>75</v>
@@ -15242,7 +15254,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E467" t="n">
         <v>68</v>
@@ -15273,7 +15285,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E468" t="n">
         <v>192</v>
@@ -15304,7 +15316,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E469" t="n">
         <v>69</v>
@@ -15335,7 +15347,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E470" t="n">
         <v>193</v>
@@ -15366,10 +15378,10 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E471" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F471" t="n">
         <v>0</v>
@@ -15397,7 +15409,7 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E472" t="n">
         <v>194</v>
@@ -15428,10 +15440,10 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E473" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F473" t="n">
         <v>0</v>
@@ -15459,7 +15471,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E474" t="n">
         <v>76</v>
@@ -15490,7 +15502,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E475" t="n">
         <v>77</v>
@@ -15521,7 +15533,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E476" t="n">
         <v>70</v>
@@ -15552,7 +15564,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E477" t="n">
         <v>78</v>
@@ -15583,10 +15595,10 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E478" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F478" t="n">
         <v>0</v>
@@ -15614,7 +15626,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E479" t="n">
         <v>195</v>
@@ -15645,10 +15657,10 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E480" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F480" t="n">
         <v>0</v>
@@ -15676,7 +15688,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E481" t="n">
         <v>196</v>
@@ -15707,10 +15719,10 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E482" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F482" t="n">
         <v>0</v>
@@ -15738,10 +15750,10 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E483" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F483" t="n">
         <v>0</v>
@@ -15769,7 +15781,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E484" t="n">
         <v>79</v>
@@ -15800,7 +15812,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E485" t="n">
         <v>80</v>
@@ -15831,7 +15843,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E486" t="n">
         <v>197</v>
@@ -15862,7 +15874,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E487" t="n">
         <v>198</v>
@@ -15893,7 +15905,7 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E488" t="n">
         <v>199</v>
@@ -15924,7 +15936,7 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E489" t="n">
         <v>200</v>
@@ -15955,7 +15967,7 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E490" t="n">
         <v>201</v>
@@ -15986,7 +15998,7 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E491" t="n">
         <v>202</v>
@@ -16017,10 +16029,10 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E492" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F492" t="n">
         <v>0</v>
@@ -16048,7 +16060,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E493" t="n">
         <v>81</v>
@@ -16079,7 +16091,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E494" t="n">
         <v>203</v>
@@ -16110,7 +16122,7 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E495" t="n">
         <v>204</v>
@@ -16141,10 +16153,10 @@
         </is>
       </c>
       <c r="D496" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E496" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F496" t="n">
         <v>0</v>
@@ -16172,7 +16184,7 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E497" t="n">
         <v>71</v>
@@ -16203,7 +16215,7 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E498" t="n">
         <v>82</v>
@@ -16234,7 +16246,7 @@
         </is>
       </c>
       <c r="D499" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E499" t="n">
         <v>205</v>
@@ -16265,7 +16277,7 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E500" t="n">
         <v>83</v>
@@ -16296,7 +16308,7 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E501" t="n">
         <v>84</v>
@@ -16327,10 +16339,10 @@
         </is>
       </c>
       <c r="D502" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E502" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F502" t="n">
         <v>0</v>
@@ -16358,10 +16370,10 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E503" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F503" t="n">
         <v>0</v>
@@ -16389,7 +16401,7 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E504" t="n">
         <v>206</v>
@@ -16420,7 +16432,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E505" t="n">
         <v>207</v>
@@ -16451,7 +16463,7 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E506" t="n">
         <v>208</v>
@@ -16482,10 +16494,10 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E507" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F507" t="n">
         <v>0</v>
@@ -16513,7 +16525,7 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E508" t="n">
         <v>209</v>
@@ -16544,7 +16556,7 @@
         </is>
       </c>
       <c r="D509" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E509" t="n">
         <v>210</v>
@@ -16575,7 +16587,7 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E510" t="n">
         <v>85</v>
@@ -16606,7 +16618,7 @@
         </is>
       </c>
       <c r="D511" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E511" t="n">
         <v>86</v>
@@ -16637,7 +16649,7 @@
         </is>
       </c>
       <c r="D512" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E512" t="n">
         <v>87</v>
@@ -16668,7 +16680,7 @@
         </is>
       </c>
       <c r="D513" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E513" t="n">
         <v>72</v>
@@ -16699,7 +16711,7 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E514" t="n">
         <v>211</v>
@@ -16730,7 +16742,7 @@
         </is>
       </c>
       <c r="D515" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E515" t="n">
         <v>73</v>
@@ -16761,7 +16773,7 @@
         </is>
       </c>
       <c r="D516" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E516" t="n">
         <v>88</v>
@@ -16792,7 +16804,7 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E517" t="n">
         <v>212</v>
@@ -16823,7 +16835,7 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E518" t="n">
         <v>213</v>
@@ -16854,10 +16866,10 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E519" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F519" t="n">
         <v>0</v>
@@ -16885,7 +16897,7 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E520" t="n">
         <v>89</v>
@@ -16916,7 +16928,7 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E521" t="n">
         <v>214</v>
@@ -16947,7 +16959,7 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E522" t="n">
         <v>215</v>
@@ -16978,7 +16990,7 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E523" t="n">
         <v>216</v>
@@ -17009,10 +17021,10 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E524" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F524" t="n">
         <v>0</v>
@@ -17040,10 +17052,10 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E525" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F525" t="n">
         <v>0</v>
@@ -17071,10 +17083,10 @@
         </is>
       </c>
       <c r="D526" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E526" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F526" t="n">
         <v>0</v>
@@ -17102,7 +17114,7 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E527" t="n">
         <v>217</v>
@@ -17133,7 +17145,7 @@
         </is>
       </c>
       <c r="D528" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E528" t="n">
         <v>218</v>
@@ -17164,7 +17176,7 @@
         </is>
       </c>
       <c r="D529" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E529" t="n">
         <v>74</v>
@@ -17195,7 +17207,7 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E530" t="n">
         <v>219</v>
@@ -17226,7 +17238,7 @@
         </is>
       </c>
       <c r="D531" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E531" t="n">
         <v>220</v>
@@ -17257,7 +17269,7 @@
         </is>
       </c>
       <c r="D532" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E532" t="n">
         <v>221</v>
@@ -17288,7 +17300,7 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E533" t="n">
         <v>222</v>
@@ -17319,7 +17331,7 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E534" t="n">
         <v>90</v>
@@ -17350,7 +17362,7 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E535" t="n">
         <v>223</v>
@@ -17381,7 +17393,7 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E536" t="n">
         <v>75</v>
@@ -17412,10 +17424,10 @@
         </is>
       </c>
       <c r="D537" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E537" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F537" t="n">
         <v>0</v>
@@ -17443,10 +17455,10 @@
         </is>
       </c>
       <c r="D538" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E538" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F538" t="n">
         <v>0</v>
@@ -17474,10 +17486,10 @@
         </is>
       </c>
       <c r="D539" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E539" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F539" t="n">
         <v>0</v>
@@ -17505,7 +17517,7 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E540" t="n">
         <v>224</v>
@@ -17536,7 +17548,7 @@
         </is>
       </c>
       <c r="D541" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E541" t="n">
         <v>91</v>
@@ -17567,7 +17579,7 @@
         </is>
       </c>
       <c r="D542" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E542" t="n">
         <v>225</v>
@@ -17598,7 +17610,7 @@
         </is>
       </c>
       <c r="D543" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E543" t="n">
         <v>226</v>
@@ -17629,7 +17641,7 @@
         </is>
       </c>
       <c r="D544" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E544" t="n">
         <v>76</v>
@@ -17660,7 +17672,7 @@
         </is>
       </c>
       <c r="D545" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E545" t="n">
         <v>227</v>
@@ -17691,7 +17703,7 @@
         </is>
       </c>
       <c r="D546" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E546" t="n">
         <v>228</v>
@@ -17722,7 +17734,7 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E547" t="n">
         <v>77</v>
@@ -17753,7 +17765,7 @@
         </is>
       </c>
       <c r="D548" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E548" t="n">
         <v>229</v>
@@ -17784,7 +17796,7 @@
         </is>
       </c>
       <c r="D549" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E549" t="n">
         <v>230</v>
@@ -17815,7 +17827,7 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E550" t="n">
         <v>78</v>
@@ -17846,7 +17858,7 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E551" t="n">
         <v>92</v>
@@ -17877,7 +17889,7 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E552" t="n">
         <v>231</v>
@@ -17908,7 +17920,7 @@
         </is>
       </c>
       <c r="D553" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E553" t="n">
         <v>232</v>
@@ -17939,7 +17951,7 @@
         </is>
       </c>
       <c r="D554" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E554" t="n">
         <v>233</v>
@@ -17970,7 +17982,7 @@
         </is>
       </c>
       <c r="D555" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E555" t="n">
         <v>234</v>
@@ -18001,7 +18013,7 @@
         </is>
       </c>
       <c r="D556" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E556" t="n">
         <v>235</v>
@@ -18032,10 +18044,10 @@
         </is>
       </c>
       <c r="D557" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E557" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F557" t="n">
         <v>0</v>
@@ -18063,7 +18075,7 @@
         </is>
       </c>
       <c r="D558" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E558" t="n">
         <v>93</v>
@@ -18094,10 +18106,10 @@
         </is>
       </c>
       <c r="D559" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E559" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F559" t="n">
         <v>0</v>
@@ -18125,10 +18137,10 @@
         </is>
       </c>
       <c r="D560" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E560" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F560" t="n">
         <v>0</v>
@@ -18156,7 +18168,7 @@
         </is>
       </c>
       <c r="D561" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E561" t="n">
         <v>236</v>
@@ -18187,7 +18199,7 @@
         </is>
       </c>
       <c r="D562" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E562" t="n">
         <v>94</v>
@@ -18218,10 +18230,10 @@
         </is>
       </c>
       <c r="D563" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E563" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F563" t="n">
         <v>0</v>
@@ -18249,7 +18261,7 @@
         </is>
       </c>
       <c r="D564" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E564" t="n">
         <v>237</v>
@@ -18280,7 +18292,7 @@
         </is>
       </c>
       <c r="D565" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E565" t="n">
         <v>79</v>
@@ -18311,7 +18323,7 @@
         </is>
       </c>
       <c r="D566" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E566" t="n">
         <v>238</v>
@@ -18342,7 +18354,7 @@
         </is>
       </c>
       <c r="D567" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E567" t="n">
         <v>80</v>
@@ -18373,7 +18385,7 @@
         </is>
       </c>
       <c r="D568" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E568" t="n">
         <v>239</v>
@@ -18404,7 +18416,7 @@
         </is>
       </c>
       <c r="D569" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E569" t="n">
         <v>95</v>
@@ -18435,7 +18447,7 @@
         </is>
       </c>
       <c r="D570" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E570" t="n">
         <v>240</v>
@@ -18466,7 +18478,7 @@
         </is>
       </c>
       <c r="D571" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E571" t="n">
         <v>241</v>
@@ -18497,10 +18509,10 @@
         </is>
       </c>
       <c r="D572" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E572" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F572" t="n">
         <v>0</v>
@@ -18528,7 +18540,7 @@
         </is>
       </c>
       <c r="D573" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E573" t="n">
         <v>96</v>
@@ -18559,7 +18571,7 @@
         </is>
       </c>
       <c r="D574" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E574" t="n">
         <v>242</v>
@@ -18590,7 +18602,7 @@
         </is>
       </c>
       <c r="D575" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E575" t="n">
         <v>243</v>
@@ -18621,10 +18633,10 @@
         </is>
       </c>
       <c r="D576" t="n">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E576" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F576" t="n">
         <v>0</v>
@@ -18652,7 +18664,7 @@
         </is>
       </c>
       <c r="D577" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E577" t="n">
         <v>97</v>
@@ -18683,7 +18695,7 @@
         </is>
       </c>
       <c r="D578" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E578" t="n">
         <v>98</v>
@@ -18714,7 +18726,7 @@
         </is>
       </c>
       <c r="D579" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E579" t="n">
         <v>244</v>
@@ -18745,7 +18757,7 @@
         </is>
       </c>
       <c r="D580" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E580" t="n">
         <v>81</v>
@@ -18776,7 +18788,7 @@
         </is>
       </c>
       <c r="D581" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E581" t="n">
         <v>99</v>
@@ -18807,7 +18819,7 @@
         </is>
       </c>
       <c r="D582" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E582" t="n">
         <v>82</v>
@@ -18838,7 +18850,7 @@
         </is>
       </c>
       <c r="D583" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E583" t="n">
         <v>100</v>
@@ -18869,7 +18881,7 @@
         </is>
       </c>
       <c r="D584" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E584" t="n">
         <v>101</v>
@@ -18900,7 +18912,7 @@
         </is>
       </c>
       <c r="D585" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E585" t="n">
         <v>102</v>
@@ -18931,10 +18943,10 @@
         </is>
       </c>
       <c r="D586" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E586" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F586" t="n">
         <v>0</v>
@@ -18962,7 +18974,7 @@
         </is>
       </c>
       <c r="D587" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E587" t="n">
         <v>103</v>
@@ -18993,7 +19005,7 @@
         </is>
       </c>
       <c r="D588" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E588" t="n">
         <v>245</v>
@@ -19024,7 +19036,7 @@
         </is>
       </c>
       <c r="D589" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E589" t="n">
         <v>83</v>
@@ -19055,7 +19067,7 @@
         </is>
       </c>
       <c r="D590" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E590" t="n">
         <v>104</v>
@@ -19086,10 +19098,10 @@
         </is>
       </c>
       <c r="D591" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E591" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F591" t="n">
         <v>0</v>
@@ -19117,7 +19129,7 @@
         </is>
       </c>
       <c r="D592" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E592" t="n">
         <v>246</v>
@@ -19148,10 +19160,10 @@
         </is>
       </c>
       <c r="D593" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E593" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F593" t="n">
         <v>0</v>
@@ -19179,7 +19191,7 @@
         </is>
       </c>
       <c r="D594" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E594" t="n">
         <v>247</v>
@@ -19210,10 +19222,10 @@
         </is>
       </c>
       <c r="D595" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E595" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F595" t="n">
         <v>0</v>
@@ -19241,7 +19253,7 @@
         </is>
       </c>
       <c r="D596" t="n">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E596" t="n">
         <v>84</v>
@@ -19272,7 +19284,7 @@
         </is>
       </c>
       <c r="D597" t="n">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E597" t="n">
         <v>85</v>
@@ -19303,7 +19315,7 @@
         </is>
       </c>
       <c r="D598" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E598" t="n">
         <v>86</v>
@@ -19334,10 +19346,10 @@
         </is>
       </c>
       <c r="D599" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E599" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F599" t="n">
         <v>0</v>
@@ -19365,7 +19377,7 @@
         </is>
       </c>
       <c r="D600" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E600" t="n">
         <v>105</v>
@@ -19396,7 +19408,7 @@
         </is>
       </c>
       <c r="D601" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E601" t="n">
         <v>248</v>
@@ -19427,7 +19439,7 @@
         </is>
       </c>
       <c r="D602" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E602" t="n">
         <v>249</v>
@@ -19458,7 +19470,7 @@
         </is>
       </c>
       <c r="D603" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E603" t="n">
         <v>250</v>
@@ -19489,7 +19501,7 @@
         </is>
       </c>
       <c r="D604" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E604" t="n">
         <v>106</v>
@@ -19520,10 +19532,10 @@
         </is>
       </c>
       <c r="D605" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E605" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F605" t="n">
         <v>0</v>
@@ -19551,7 +19563,7 @@
         </is>
       </c>
       <c r="D606" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E606" t="n">
         <v>87</v>
@@ -19582,10 +19594,10 @@
         </is>
       </c>
       <c r="D607" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E607" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F607" t="n">
         <v>0</v>
@@ -19613,10 +19625,10 @@
         </is>
       </c>
       <c r="D608" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E608" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F608" t="n">
         <v>0</v>
@@ -19644,7 +19656,7 @@
         </is>
       </c>
       <c r="D609" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E609" t="n">
         <v>251</v>
@@ -19675,10 +19687,10 @@
         </is>
       </c>
       <c r="D610" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E610" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F610" t="n">
         <v>0</v>
@@ -19706,7 +19718,7 @@
         </is>
       </c>
       <c r="D611" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E611" t="n">
         <v>107</v>
@@ -19737,7 +19749,7 @@
         </is>
       </c>
       <c r="D612" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E612" t="n">
         <v>108</v>
@@ -19768,7 +19780,7 @@
         </is>
       </c>
       <c r="D613" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E613" t="n">
         <v>252</v>
@@ -19799,7 +19811,7 @@
         </is>
       </c>
       <c r="D614" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E614" t="n">
         <v>88</v>
@@ -19830,10 +19842,10 @@
         </is>
       </c>
       <c r="D615" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E615" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F615" t="n">
         <v>0</v>
@@ -19861,7 +19873,7 @@
         </is>
       </c>
       <c r="D616" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E616" t="n">
         <v>89</v>
@@ -19892,7 +19904,7 @@
         </is>
       </c>
       <c r="D617" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E617" t="n">
         <v>109</v>
@@ -19923,7 +19935,7 @@
         </is>
       </c>
       <c r="D618" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E618" t="n">
         <v>253</v>
@@ -19954,7 +19966,7 @@
         </is>
       </c>
       <c r="D619" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E619" t="n">
         <v>254</v>
@@ -19985,10 +19997,10 @@
         </is>
       </c>
       <c r="D620" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E620" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F620" t="n">
         <v>0</v>
@@ -20016,7 +20028,7 @@
         </is>
       </c>
       <c r="D621" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E621" t="n">
         <v>90</v>
@@ -20047,7 +20059,7 @@
         </is>
       </c>
       <c r="D622" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E622" t="n">
         <v>255</v>
@@ -20078,10 +20090,10 @@
         </is>
       </c>
       <c r="D623" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E623" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F623" t="n">
         <v>0</v>
@@ -20109,7 +20121,7 @@
         </is>
       </c>
       <c r="D624" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E624" t="n">
         <v>110</v>
@@ -20140,7 +20152,7 @@
         </is>
       </c>
       <c r="D625" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E625" t="n">
         <v>256</v>
@@ -20171,7 +20183,7 @@
         </is>
       </c>
       <c r="D626" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E626" t="n">
         <v>111</v>
@@ -20202,7 +20214,7 @@
         </is>
       </c>
       <c r="D627" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E627" t="n">
         <v>112</v>
@@ -20233,7 +20245,7 @@
         </is>
       </c>
       <c r="D628" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E628" t="n">
         <v>257</v>
@@ -20264,7 +20276,7 @@
         </is>
       </c>
       <c r="D629" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E629" t="n">
         <v>113</v>
@@ -20295,7 +20307,7 @@
         </is>
       </c>
       <c r="D630" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E630" t="n">
         <v>258</v>
@@ -20326,7 +20338,7 @@
         </is>
       </c>
       <c r="D631" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E631" t="n">
         <v>259</v>
@@ -20357,7 +20369,7 @@
         </is>
       </c>
       <c r="D632" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E632" t="n">
         <v>260</v>
@@ -20388,7 +20400,7 @@
         </is>
       </c>
       <c r="D633" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E633" t="n">
         <v>261</v>
@@ -20419,7 +20431,7 @@
         </is>
       </c>
       <c r="D634" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E634" t="n">
         <v>114</v>
@@ -20450,10 +20462,10 @@
         </is>
       </c>
       <c r="D635" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E635" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F635" t="n">
         <v>0</v>
@@ -20481,7 +20493,7 @@
         </is>
       </c>
       <c r="D636" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E636" t="n">
         <v>262</v>
@@ -20512,7 +20524,7 @@
         </is>
       </c>
       <c r="D637" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E637" t="n">
         <v>263</v>
@@ -20543,10 +20555,10 @@
         </is>
       </c>
       <c r="D638" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E638" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F638" t="n">
         <v>0</v>
@@ -20574,7 +20586,7 @@
         </is>
       </c>
       <c r="D639" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E639" t="n">
         <v>115</v>
@@ -20605,7 +20617,7 @@
         </is>
       </c>
       <c r="D640" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E640" t="n">
         <v>264</v>
@@ -20636,7 +20648,7 @@
         </is>
       </c>
       <c r="D641" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E641" t="n">
         <v>265</v>
@@ -20667,7 +20679,7 @@
         </is>
       </c>
       <c r="D642" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E642" t="n">
         <v>266</v>
@@ -20698,7 +20710,7 @@
         </is>
       </c>
       <c r="D643" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E643" t="n">
         <v>91</v>
@@ -20729,7 +20741,7 @@
         </is>
       </c>
       <c r="D644" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E644" t="n">
         <v>116</v>
@@ -20760,10 +20772,10 @@
         </is>
       </c>
       <c r="D645" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E645" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F645" t="n">
         <v>0</v>
@@ -20791,7 +20803,7 @@
         </is>
       </c>
       <c r="D646" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E646" t="n">
         <v>267</v>
@@ -20822,10 +20834,10 @@
         </is>
       </c>
       <c r="D647" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E647" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F647" t="n">
         <v>0</v>
@@ -20853,7 +20865,7 @@
         </is>
       </c>
       <c r="D648" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E648" t="n">
         <v>268</v>
@@ -20884,7 +20896,7 @@
         </is>
       </c>
       <c r="D649" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E649" t="n">
         <v>269</v>
@@ -20915,10 +20927,10 @@
         </is>
       </c>
       <c r="D650" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E650" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F650" t="n">
         <v>0</v>
@@ -20946,7 +20958,7 @@
         </is>
       </c>
       <c r="D651" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E651" t="n">
         <v>270</v>
@@ -20977,7 +20989,7 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E652" t="n">
         <v>117</v>
@@ -21008,7 +21020,7 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E653" t="n">
         <v>271</v>
@@ -21039,7 +21051,7 @@
         </is>
       </c>
       <c r="D654" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E654" t="n">
         <v>118</v>
@@ -21070,10 +21082,10 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E655" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F655" t="n">
         <v>0</v>
@@ -21101,7 +21113,7 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E656" t="n">
         <v>272</v>
@@ -21132,7 +21144,7 @@
         </is>
       </c>
       <c r="D657" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E657" t="n">
         <v>273</v>
@@ -21163,7 +21175,7 @@
         </is>
       </c>
       <c r="D658" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E658" t="n">
         <v>119</v>
@@ -21194,7 +21206,7 @@
         </is>
       </c>
       <c r="D659" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E659" t="n">
         <v>274</v>
@@ -21225,7 +21237,7 @@
         </is>
       </c>
       <c r="D660" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E660" t="n">
         <v>275</v>
@@ -21256,7 +21268,7 @@
         </is>
       </c>
       <c r="D661" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E661" t="n">
         <v>276</v>
@@ -21287,10 +21299,10 @@
         </is>
       </c>
       <c r="D662" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E662" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F662" t="n">
         <v>0</v>
@@ -21318,10 +21330,10 @@
         </is>
       </c>
       <c r="D663" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E663" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F663" t="n">
         <v>0</v>
@@ -21349,7 +21361,7 @@
         </is>
       </c>
       <c r="D664" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E664" t="n">
         <v>120</v>
@@ -21380,7 +21392,7 @@
         </is>
       </c>
       <c r="D665" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E665" t="n">
         <v>277</v>
@@ -21411,10 +21423,10 @@
         </is>
       </c>
       <c r="D666" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E666" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F666" t="n">
         <v>0</v>
@@ -21442,7 +21454,7 @@
         </is>
       </c>
       <c r="D667" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E667" t="n">
         <v>92</v>
@@ -21473,7 +21485,7 @@
         </is>
       </c>
       <c r="D668" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E668" t="n">
         <v>121</v>
@@ -21504,7 +21516,7 @@
         </is>
       </c>
       <c r="D669" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E669" t="n">
         <v>122</v>
@@ -21535,7 +21547,7 @@
         </is>
       </c>
       <c r="D670" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E670" t="n">
         <v>278</v>
@@ -21566,7 +21578,7 @@
         </is>
       </c>
       <c r="D671" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E671" t="n">
         <v>123</v>
@@ -21597,7 +21609,7 @@
         </is>
       </c>
       <c r="D672" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E672" t="n">
         <v>93</v>
@@ -21628,10 +21640,10 @@
         </is>
       </c>
       <c r="D673" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E673" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F673" t="n">
         <v>0</v>
@@ -21659,7 +21671,7 @@
         </is>
       </c>
       <c r="D674" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E674" t="n">
         <v>124</v>
@@ -21690,7 +21702,7 @@
         </is>
       </c>
       <c r="D675" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E675" t="n">
         <v>279</v>
@@ -21721,7 +21733,7 @@
         </is>
       </c>
       <c r="D676" t="n">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E676" t="n">
         <v>280</v>
@@ -21752,7 +21764,7 @@
         </is>
       </c>
       <c r="D677" t="n">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E677" t="n">
         <v>281</v>
@@ -21783,10 +21795,10 @@
         </is>
       </c>
       <c r="D678" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E678" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F678" t="n">
         <v>0</v>
@@ -21814,7 +21826,7 @@
         </is>
       </c>
       <c r="D679" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E679" t="n">
         <v>282</v>
@@ -21845,7 +21857,7 @@
         </is>
       </c>
       <c r="D680" t="n">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E680" t="n">
         <v>125</v>
@@ -21876,7 +21888,7 @@
         </is>
       </c>
       <c r="D681" t="n">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E681" t="n">
         <v>283</v>
@@ -21907,10 +21919,10 @@
         </is>
       </c>
       <c r="D682" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E682" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F682" t="n">
         <v>0</v>
@@ -21938,7 +21950,7 @@
         </is>
       </c>
       <c r="D683" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E683" t="n">
         <v>284</v>
@@ -21969,7 +21981,7 @@
         </is>
       </c>
       <c r="D684" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E684" t="n">
         <v>126</v>
@@ -22000,10 +22012,10 @@
         </is>
       </c>
       <c r="D685" t="n">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E685" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F685" t="n">
         <v>0</v>
@@ -22031,7 +22043,7 @@
         </is>
       </c>
       <c r="D686" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E686" t="n">
         <v>127</v>
@@ -22062,7 +22074,7 @@
         </is>
       </c>
       <c r="D687" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E687" t="n">
         <v>128</v>
@@ -22093,10 +22105,10 @@
         </is>
       </c>
       <c r="D688" t="n">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E688" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F688" t="n">
         <v>0</v>
@@ -22124,7 +22136,7 @@
         </is>
       </c>
       <c r="D689" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E689" t="n">
         <v>129</v>
@@ -22155,7 +22167,7 @@
         </is>
       </c>
       <c r="D690" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E690" t="n">
         <v>285</v>
@@ -22186,10 +22198,10 @@
         </is>
       </c>
       <c r="D691" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E691" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F691" t="n">
         <v>0</v>
@@ -22217,7 +22229,7 @@
         </is>
       </c>
       <c r="D692" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E692" t="n">
         <v>94</v>
@@ -22248,7 +22260,7 @@
         </is>
       </c>
       <c r="D693" t="n">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E693" t="n">
         <v>286</v>
@@ -22279,7 +22291,7 @@
         </is>
       </c>
       <c r="D694" t="n">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E694" t="n">
         <v>287</v>
@@ -22310,7 +22322,7 @@
         </is>
       </c>
       <c r="D695" t="n">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E695" t="n">
         <v>130</v>
@@ -22341,10 +22353,10 @@
         </is>
       </c>
       <c r="D696" t="n">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E696" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F696" t="n">
         <v>0</v>
@@ -22372,7 +22384,7 @@
         </is>
       </c>
       <c r="D697" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E697" t="n">
         <v>288</v>
@@ -22403,7 +22415,7 @@
         </is>
       </c>
       <c r="D698" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E698" t="n">
         <v>289</v>
@@ -22434,7 +22446,7 @@
         </is>
       </c>
       <c r="D699" t="n">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E699" t="n">
         <v>290</v>
@@ -22465,7 +22477,7 @@
         </is>
       </c>
       <c r="D700" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E700" t="n">
         <v>291</v>
@@ -22496,10 +22508,10 @@
         </is>
       </c>
       <c r="D701" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E701" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F701" t="n">
         <v>0</v>
@@ -22527,7 +22539,7 @@
         </is>
       </c>
       <c r="D702" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E702" t="n">
         <v>95</v>
@@ -22558,10 +22570,10 @@
         </is>
       </c>
       <c r="D703" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E703" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F703" t="n">
         <v>0</v>
@@ -22589,7 +22601,7 @@
         </is>
       </c>
       <c r="D704" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E704" t="n">
         <v>292</v>
@@ -22620,7 +22632,7 @@
         </is>
       </c>
       <c r="D705" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E705" t="n">
         <v>293</v>
@@ -22651,10 +22663,10 @@
         </is>
       </c>
       <c r="D706" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E706" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F706" t="n">
         <v>0</v>
@@ -22682,7 +22694,7 @@
         </is>
       </c>
       <c r="D707" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E707" t="n">
         <v>131</v>
@@ -22713,10 +22725,10 @@
         </is>
       </c>
       <c r="D708" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E708" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F708" t="n">
         <v>0</v>
@@ -22744,7 +22756,7 @@
         </is>
       </c>
       <c r="D709" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E709" t="n">
         <v>294</v>
@@ -22775,10 +22787,10 @@
         </is>
       </c>
       <c r="D710" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E710" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F710" t="n">
         <v>0</v>
@@ -22806,10 +22818,10 @@
         </is>
       </c>
       <c r="D711" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E711" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F711" t="n">
         <v>0</v>
@@ -22837,7 +22849,7 @@
         </is>
       </c>
       <c r="D712" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E712" t="n">
         <v>295</v>
@@ -22868,7 +22880,7 @@
         </is>
       </c>
       <c r="D713" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E713" t="n">
         <v>132</v>
@@ -22899,7 +22911,7 @@
         </is>
       </c>
       <c r="D714" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E714" t="n">
         <v>96</v>
@@ -22930,7 +22942,7 @@
         </is>
       </c>
       <c r="D715" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E715" t="n">
         <v>133</v>
@@ -22961,7 +22973,7 @@
         </is>
       </c>
       <c r="D716" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E716" t="n">
         <v>296</v>
@@ -22992,7 +23004,7 @@
         </is>
       </c>
       <c r="D717" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E717" t="n">
         <v>297</v>
@@ -23023,7 +23035,7 @@
         </is>
       </c>
       <c r="D718" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E718" t="n">
         <v>134</v>
@@ -23054,7 +23066,7 @@
         </is>
       </c>
       <c r="D719" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E719" t="n">
         <v>135</v>
@@ -23085,10 +23097,10 @@
         </is>
       </c>
       <c r="D720" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E720" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F720" t="n">
         <v>0</v>
@@ -23116,7 +23128,7 @@
         </is>
       </c>
       <c r="D721" t="n">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E721" t="n">
         <v>298</v>
@@ -23147,10 +23159,10 @@
         </is>
       </c>
       <c r="D722" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E722" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F722" t="n">
         <v>0</v>
@@ -23178,7 +23190,7 @@
         </is>
       </c>
       <c r="D723" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E723" t="n">
         <v>299</v>
@@ -23209,7 +23221,7 @@
         </is>
       </c>
       <c r="D724" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E724" t="n">
         <v>136</v>
@@ -23240,7 +23252,7 @@
         </is>
       </c>
       <c r="D725" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E725" t="n">
         <v>137</v>
@@ -23271,7 +23283,7 @@
         </is>
       </c>
       <c r="D726" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E726" t="n">
         <v>138</v>
@@ -23302,7 +23314,7 @@
         </is>
       </c>
       <c r="D727" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E727" t="n">
         <v>300</v>
@@ -23333,7 +23345,7 @@
         </is>
       </c>
       <c r="D728" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E728" t="n">
         <v>301</v>
@@ -23364,18 +23376,21 @@
         </is>
       </c>
       <c r="D729" t="n">
-        <v>732</v>
+        <v>120</v>
       </c>
       <c r="E729" t="n">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="F729" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G729" t="inlineStr">
         <is>
           <t>12495</t>
         </is>
+      </c>
+      <c r="H729" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="730">

--- a/players.xlsx
+++ b/players.xlsx
@@ -543,13 +543,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -855,7 +855,7 @@
         <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>7</v>
@@ -923,7 +923,7 @@
         <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>6</v>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
         <v>91</v>
@@ -1059,7 +1059,7 @@
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
         <v>80</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F25" t="n">
         <v>81</v>
@@ -1331,7 +1331,7 @@
         <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27">
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
         <v>79</v>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
         <v>22</v>
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
         <v>84</v>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E33" t="n">
         <v>3</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F34" t="n">
         <v>83</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E35" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
         <v>87</v>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
         <v>83</v>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E37" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E38" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F38" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E39" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F39" t="n">
         <v>84</v>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E40" t="n">
         <v>26</v>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E41" t="n">
         <v>20</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E43" t="n">
         <v>25</v>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E44" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F44" t="n">
         <v>84</v>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E45" t="n">
         <v>21</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E46" t="n">
         <v>14</v>
@@ -2036,13 +2036,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E47" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F47" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E48" t="n">
         <v>23</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E49" t="n">
         <v>24</v>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E50" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F50" t="n">
         <v>80</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E51" t="n">
         <v>26</v>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E52" t="n">
         <v>27</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E54" t="n">
         <v>4</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E57" t="n">
         <v>27</v>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E58" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
         <v>82</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F59" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E60" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E61" t="n">
         <v>30</v>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E64" t="n">
         <v>25</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E65" t="n">
         <v>31</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E66" t="n">
         <v>32</v>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F67" t="n">
         <v>84</v>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E68" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F68" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E69" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F69" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70">
@@ -2855,7 +2855,7 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E73" t="n">
         <v>12</v>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>83</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E78" t="n">
         <v>8</v>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E79" t="n">
         <v>33</v>
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F80" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E81" t="n">
         <v>37</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E82" t="n">
         <v>38</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E83" t="n">
         <v>30</v>
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E84" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E86" t="n">
         <v>32</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E87" t="n">
         <v>31</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E88" t="n">
         <v>39</v>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F89" t="n">
         <v>78</v>
@@ -3495,13 +3495,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F90" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E91" t="n">
         <v>34</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E93" t="n">
         <v>40</v>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F94" t="n">
         <v>65</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E95" t="n">
         <v>15</v>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E96" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E97" t="n">
         <v>35</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E98" t="n">
         <v>41</v>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E99" t="n">
         <v>42</v>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E100" t="n">
         <v>13</v>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E101" t="n">
         <v>43</v>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E102" t="n">
         <v>37</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E103" t="n">
         <v>16</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E104" t="n">
         <v>39</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E105" t="n">
         <v>46</v>
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E106" t="n">
         <v>20</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E107" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E108" t="n">
         <v>7</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E109" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E110" t="n">
         <v>36</v>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E112" t="n">
         <v>50</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E113" t="n">
         <v>40</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E114" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E115" t="n">
         <v>19</v>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E116" t="n">
         <v>41</v>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E117" t="n">
         <v>21</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E118" t="n">
         <v>42</v>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E119" t="n">
         <v>51</v>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E120" t="n">
         <v>22</v>
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E121" t="n">
         <v>43</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E122" t="n">
         <v>52</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E123" t="n">
         <v>53</v>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E124" t="n">
         <v>45</v>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E125" t="n">
         <v>23</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E126" t="n">
         <v>47</v>
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E127" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E128" t="n">
         <v>54</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E129" t="n">
         <v>55</v>
@@ -4777,10 +4777,10 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E130" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E131" t="n">
         <v>36</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E132" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E133" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E134" t="n">
         <v>48</v>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E135" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E136" t="n">
         <v>56</v>
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E138" t="n">
         <v>24</v>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E139" t="n">
         <v>49</v>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E140" t="n">
         <v>57</v>
@@ -5127,18 +5127,21 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E141" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>7002</t>
         </is>
+      </c>
+      <c r="H141" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="142">
@@ -5158,10 +5161,10 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E142" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -5189,7 +5192,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E143" t="n">
         <v>50</v>
@@ -5220,7 +5223,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E144" t="n">
         <v>25</v>
@@ -5251,7 +5254,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E145" t="n">
         <v>58</v>
@@ -5282,7 +5285,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E146" t="n">
         <v>51</v>
@@ -5316,18 +5319,21 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="E147" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
           <t>8131</t>
         </is>
+      </c>
+      <c r="H147" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="148">
@@ -6218,7 +6224,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E176" t="n">
         <v>6</v>
@@ -6810,7 +6816,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E195" t="n">
         <v>49</v>
@@ -7030,10 +7036,10 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E202" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F202" t="n">
         <v>78</v>
@@ -7064,10 +7070,10 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E203" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -7467,7 +7473,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E216" t="n">
         <v>38</v>
@@ -7622,7 +7628,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E221" t="n">
         <v>48</v>
@@ -7777,10 +7783,10 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E226" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F226" t="n">
         <v>61</v>
@@ -8090,10 +8096,10 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E236" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -8896,7 +8902,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E262" t="n">
         <v>47</v>
@@ -23376,7 +23382,7 @@
         </is>
       </c>
       <c r="D729" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E729" t="n">
         <v>44</v>
